--- a/docs/Programming Puzzles.xlsx
+++ b/docs/Programming Puzzles.xlsx
@@ -1,20 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Development\Projects\ProjectDSA\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\Projects\ProjectDSA\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A46C6958-4A4B-472E-9CE9-3BB7F6E68541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17C6764F-4D3D-4883-9E4D-0B76B36AC494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{B7950DC0-5F1E-48EF-9340-8CAB6CE423A3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{B7950DC0-5F1E-48EF-9340-8CAB6CE423A3}"/>
   </bookViews>
   <sheets>
-    <sheet name="AOC" sheetId="2" r:id="rId1"/>
-    <sheet name="Leetcode" sheetId="1" r:id="rId2"/>
+    <sheet name="Notes" sheetId="3" r:id="rId1"/>
+    <sheet name="AOC" sheetId="2" r:id="rId2"/>
+    <sheet name="Leetcode" sheetId="1" r:id="rId3"/>
+    <sheet name="Structy" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1281" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="422">
   <si>
     <t>PLATFORM</t>
   </si>
@@ -72,12 +74,6 @@
     <t>Valid Anagram</t>
   </si>
   <si>
-    <t>STATUS</t>
-  </si>
-  <si>
-    <t>SOLVED</t>
-  </si>
-  <si>
     <t>15/05/2025</t>
   </si>
   <si>
@@ -183,18 +179,12 @@
     <t>Two Pointers</t>
   </si>
   <si>
-    <t>This is a tough one. Weird pointer positioning.</t>
-  </si>
-  <si>
     <t>Container with Most Water</t>
   </si>
   <si>
     <t>30/05/2025</t>
   </si>
   <si>
-    <t>STRUGGLED</t>
-  </si>
-  <si>
     <t>Trapping Rain Water</t>
   </si>
   <si>
@@ -321,9 +311,6 @@
     <t>Easy one :-)</t>
   </si>
   <si>
-    <t>Seach a 2D Matrix</t>
-  </si>
-  <si>
     <t>Killed it.</t>
   </si>
   <si>
@@ -357,9 +344,6 @@
     <t>Median of Two Sorted Arrays</t>
   </si>
   <si>
-    <t>DEFERRED</t>
-  </si>
-  <si>
     <t>Sticking with Easy and Medium for now.</t>
   </si>
   <si>
@@ -390,9 +374,6 @@
     <t>Remove Nth Node from End of List</t>
   </si>
   <si>
-    <t>19/06/2025</t>
-  </si>
-  <si>
     <t>Linked Lists, Two Pointers</t>
   </si>
   <si>
@@ -507,9 +488,6 @@
     <t>Binary Tree Right Side View</t>
   </si>
   <si>
-    <t>Annihalited it!</t>
-  </si>
-  <si>
     <t>Count Good Nodes in Binary Tree</t>
   </si>
   <si>
@@ -591,18 +569,9 @@
     <t>K Closest Points to Origin</t>
   </si>
   <si>
-    <t>Smashed it!</t>
-  </si>
-  <si>
     <t>Kth Largest Element in an Array</t>
   </si>
   <si>
-    <t>10/07/2025</t>
-  </si>
-  <si>
-    <t>Quick Select algorithm. Can also be solved with Heaps.</t>
-  </si>
-  <si>
     <t>Task Scheduler</t>
   </si>
   <si>
@@ -645,9 +614,6 @@
     <t>Combination Sum</t>
   </si>
   <si>
-    <t>Recursion getting me. When will I get better at this?</t>
-  </si>
-  <si>
     <t>Permutations</t>
   </si>
   <si>
@@ -678,9 +644,6 @@
     <t>Palindrome Partitioning</t>
   </si>
   <si>
-    <t>17/07/2025</t>
-  </si>
-  <si>
     <t>Recursion, recursion, recursion, sigh *</t>
   </si>
   <si>
@@ -717,15 +680,6 @@
     <t>Surrounded Regions</t>
   </si>
   <si>
-    <t>18/07/2025</t>
-  </si>
-  <si>
-    <t>Easy in the end. Why do I struggle so much with this darn recursion lol</t>
-  </si>
-  <si>
-    <t>21/07/2025</t>
-  </si>
-  <si>
     <t>Beautiful code. Done using an Iterative BFS with a queue.</t>
   </si>
   <si>
@@ -750,12 +704,6 @@
     <t>25/07/2025</t>
   </si>
   <si>
-    <t>Similar to Rotting Oranges above. Reverse thinking.</t>
-  </si>
-  <si>
-    <t>26/07/2025</t>
-  </si>
-  <si>
     <t>Course Schedule II</t>
   </si>
   <si>
@@ -768,9 +716,6 @@
     <t>28/07/2025</t>
   </si>
   <si>
-    <t>Cycle detection. Directed Graph.</t>
-  </si>
-  <si>
     <t>Undirected Graph. Need to get comfortable with Union Find algorithm.</t>
   </si>
   <si>
@@ -855,9 +800,6 @@
     <t>Min Cost Climbing Stairs</t>
   </si>
   <si>
-    <t>05/08/2025</t>
-  </si>
-  <si>
     <t>Poorly worded problem. Top floor is outside bounds of array on the right.</t>
   </si>
   <si>
@@ -894,15 +836,9 @@
     <t>Decode Ways</t>
   </si>
   <si>
-    <t>09/08/2025</t>
-  </si>
-  <si>
     <t>Coin Change</t>
   </si>
   <si>
-    <t>11/08/2025</t>
-  </si>
-  <si>
     <t>I don't understand the DP solution. The DFS solution makes more sense to me.</t>
   </si>
   <si>
@@ -921,12 +857,6 @@
     <t>Word Break</t>
   </si>
   <si>
-    <t>13/08/2025</t>
-  </si>
-  <si>
-    <t>Gorgeous intuitive DP pattern. Love it.</t>
-  </si>
-  <si>
     <t>Longest Increasing Subsequence</t>
   </si>
   <si>
@@ -1219,13 +1149,169 @@
   </si>
   <si>
     <t>Python</t>
+  </si>
+  <si>
+    <t>RATING (1 - 5)</t>
+  </si>
+  <si>
+    <t>27/10/2025</t>
+  </si>
+  <si>
+    <t>Python, C#</t>
+  </si>
+  <si>
+    <t>Neetcode 150, Algomonster</t>
+  </si>
+  <si>
+    <t>In Rating 1 - 5: 1 being very hard, 5 being very easy.</t>
+  </si>
+  <si>
+    <t>Dynamic Programming, Backtracking</t>
+  </si>
+  <si>
+    <t>31/10/2025</t>
+  </si>
+  <si>
+    <t>30/10/2025</t>
+  </si>
+  <si>
+    <t>Gorgeous intuitive DP pattern. Love it. DFS with memoization.</t>
+  </si>
+  <si>
+    <t>Neetcode 150, Blind 75, Algomonster</t>
+  </si>
+  <si>
+    <t>03/11/2025</t>
+  </si>
+  <si>
+    <t>Algomonster explains and does it well.</t>
+  </si>
+  <si>
+    <t>DFS.</t>
+  </si>
+  <si>
+    <t>04/11/2025</t>
+  </si>
+  <si>
+    <t>Search a 2D Matrix</t>
+  </si>
+  <si>
+    <t>Similar to Rotting Oranges above. Reverse thinking by starting at the gates. BFS since we're looking for shortest path.</t>
+  </si>
+  <si>
+    <t>08/11/2025</t>
+  </si>
+  <si>
+    <t>07/10/2025</t>
+  </si>
+  <si>
+    <t>06/11/2025</t>
+  </si>
+  <si>
+    <t>Open the Lock</t>
+  </si>
+  <si>
+    <t>C#</t>
+  </si>
+  <si>
+    <t>10/11/2025</t>
+  </si>
+  <si>
+    <t>Implicit graph problem.</t>
+  </si>
+  <si>
+    <t>Algomonster</t>
+  </si>
+  <si>
+    <t>Sliding Puzzle</t>
+  </si>
+  <si>
+    <t>11/11/2025</t>
+  </si>
+  <si>
+    <t>Implicit graph problem. Some Math required for Serialization / Deserialization. Quite a tough one, definitely a hard problem.</t>
+  </si>
+  <si>
+    <t>Task Scheduling</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>12/11/2025</t>
+  </si>
+  <si>
+    <t>Topological Sort problem.</t>
+  </si>
+  <si>
+    <t>Reconstructing Sequence</t>
+  </si>
+  <si>
+    <t>Understanding the problem is the challenge I found.</t>
+  </si>
+  <si>
+    <t>Task Scheduling 2</t>
+  </si>
+  <si>
+    <t>13/11/2025</t>
+  </si>
+  <si>
+    <t>The parent/child relationship is important here I think in coming up with the result.</t>
+  </si>
+  <si>
+    <t>Cycle detection. Directed Graph. Topological Sort. Can also use DFS with 3 states to detect a cycle.</t>
+  </si>
+  <si>
+    <t>17/11/2025</t>
+  </si>
+  <si>
+    <t>You need to know a bit of math to calculate the Euclidean distance.</t>
+  </si>
+  <si>
+    <t>Merge K Sorted Lists</t>
+  </si>
+  <si>
+    <t>Algomonster has the 2D array and the Linked list versions.</t>
+  </si>
+  <si>
+    <t>18/11/2025</t>
+  </si>
+  <si>
+    <t>Quick Select algorithm. Can also be solved max Heap. Easy with Max Heap.</t>
+  </si>
+  <si>
+    <t>Kth Smallest Element in a Sorted Matrix</t>
+  </si>
+  <si>
+    <t>13/01/2026</t>
+  </si>
+  <si>
+    <t>Middle of a Linked List</t>
+  </si>
+  <si>
+    <t>Reverse Nodes in k-Group</t>
+  </si>
+  <si>
+    <t>Move Zeroes</t>
+  </si>
+  <si>
+    <t>14/01/2026</t>
+  </si>
+  <si>
+    <t>Maximal Square</t>
+  </si>
+  <si>
+    <t>20/01/2026</t>
+  </si>
+  <si>
+    <t>02/02/2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1255,8 +1341,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1265,8 +1365,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="1"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -1279,11 +1383,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1298,19 +1404,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="2" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="3" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="4">
+    <cellStyle name="Good" xfId="2" builtinId="26"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Neutral" xfId="3" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1642,6 +1757,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E29EE35E-42CE-4BB8-BA9B-83E0DF36D658}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="65.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>374</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{673553DD-7322-43E4-B8E6-8596552AA633}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1650,19 +1783,19 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{758F6333-ADD2-4F62-82FC-3789A0207F8D}">
-  <dimension ref="A1:J154"/>
+  <dimension ref="A1:J162"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.42578125" customWidth="1"/>
     <col min="2" max="2" width="11.85546875" style="4" customWidth="1"/>
     <col min="3" max="3" width="52.28515625" customWidth="1"/>
-    <col min="4" max="4" width="26.85546875" customWidth="1"/>
+    <col min="4" max="4" width="36.42578125" customWidth="1"/>
     <col min="5" max="5" width="13.5703125" customWidth="1"/>
-    <col min="6" max="6" width="23.7109375" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="34.5703125" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="15.28515625" customWidth="1"/>
     <col min="10" max="10" width="92.7109375" style="5" customWidth="1"/>
   </cols>
@@ -1683,20 +1816,20 @@
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>392</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>11</v>
+        <v>368</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -1710,22 +1843,19 @@
         <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
-      <c r="F2" t="s">
-        <v>40</v>
-      </c>
       <c r="G2" t="s">
-        <v>393</v>
+        <v>38</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -1739,52 +1869,50 @@
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" t="s">
-        <v>7</v>
-      </c>
       <c r="G3" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H3" t="s">
+        <v>369</v>
+      </c>
+      <c r="I3" t="s">
         <v>12</v>
       </c>
-      <c r="I3" t="s">
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="8">
+        <v>1</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="D4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" t="s">
-        <v>393</v>
-      </c>
-      <c r="H4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" t="s">
-        <v>17</v>
-      </c>
+      <c r="F4" s="8">
+        <v>5</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="J4" s="9"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -1794,25 +1922,22 @@
         <v>49</v>
       </c>
       <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
         <v>18</v>
       </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
       <c r="E5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G5" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H5" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -1823,28 +1948,25 @@
         <v>347</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>266</v>
+        <v>247</v>
       </c>
       <c r="E6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" t="s">
+        <v>369</v>
+      </c>
+      <c r="I6" t="s">
         <v>21</v>
       </c>
-      <c r="F6" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6" t="s">
-        <v>393</v>
-      </c>
-      <c r="H6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="J6" s="5" t="s">
         <v>23</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -1855,25 +1977,22 @@
         <v>238</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H7" t="s">
+        <v>369</v>
+      </c>
+      <c r="I7" t="s">
         <v>21</v>
-      </c>
-      <c r="F7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G7" t="s">
-        <v>393</v>
-      </c>
-      <c r="H7" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -1884,28 +2003,25 @@
         <v>36</v>
       </c>
       <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
         <v>28</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s">
+        <v>7</v>
+      </c>
+      <c r="H8" t="s">
+        <v>369</v>
+      </c>
+      <c r="I8" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="E8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" t="s">
-        <v>7</v>
-      </c>
-      <c r="G8" t="s">
-        <v>393</v>
-      </c>
-      <c r="H8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8" t="s">
-        <v>29</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -1916,28 +2032,25 @@
         <v>271</v>
       </c>
       <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" t="s">
+        <v>186</v>
+      </c>
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H9" t="s">
+        <v>369</v>
+      </c>
+      <c r="I9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="D9" t="s">
-        <v>197</v>
-      </c>
-      <c r="E9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" t="s">
-        <v>7</v>
-      </c>
-      <c r="G9" t="s">
-        <v>393</v>
-      </c>
-      <c r="H9" t="s">
-        <v>12</v>
-      </c>
-      <c r="I9" t="s">
-        <v>34</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -1948,28 +2061,25 @@
         <v>128</v>
       </c>
       <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" t="s">
+        <v>185</v>
+      </c>
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H10" t="s">
+        <v>369</v>
+      </c>
+      <c r="I10" t="s">
+        <v>35</v>
+      </c>
+      <c r="J10" s="5" t="s">
         <v>36</v>
-      </c>
-      <c r="D10" t="s">
-        <v>196</v>
-      </c>
-      <c r="E10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" t="s">
-        <v>7</v>
-      </c>
-      <c r="G10" t="s">
-        <v>393</v>
-      </c>
-      <c r="H10" t="s">
-        <v>12</v>
-      </c>
-      <c r="I10" t="s">
-        <v>37</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -1980,28 +2090,25 @@
         <v>125</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
       </c>
-      <c r="F11" t="s">
-        <v>40</v>
-      </c>
       <c r="G11" t="s">
-        <v>393</v>
+        <v>38</v>
       </c>
       <c r="H11" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -2012,60 +2119,57 @@
         <v>167</v>
       </c>
       <c r="C12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" t="s">
+        <v>7</v>
+      </c>
+      <c r="H12" t="s">
+        <v>369</v>
+      </c>
+      <c r="I12" t="s">
         <v>42</v>
       </c>
-      <c r="D12" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G12" t="s">
-        <v>393</v>
-      </c>
-      <c r="H12" t="s">
-        <v>12</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="J12" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="11">
+        <v>15</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="11">
+        <v>3</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="I13" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="J12" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="4">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" t="s">
-        <v>47</v>
-      </c>
-      <c r="E13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F13" t="s">
-        <v>7</v>
-      </c>
-      <c r="G13" t="s">
-        <v>393</v>
-      </c>
-      <c r="H13" t="s">
-        <v>51</v>
-      </c>
-      <c r="I13" t="s">
-        <v>46</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>48</v>
+      <c r="J13" s="12" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -2076,25 +2180,22 @@
         <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" t="s">
+        <v>19</v>
+      </c>
+      <c r="G14" t="s">
+        <v>7</v>
+      </c>
+      <c r="H14" t="s">
+        <v>369</v>
+      </c>
+      <c r="I14" t="s">
         <v>47</v>
-      </c>
-      <c r="E14" t="s">
-        <v>21</v>
-      </c>
-      <c r="F14" t="s">
-        <v>7</v>
-      </c>
-      <c r="G14" t="s">
-        <v>393</v>
-      </c>
-      <c r="H14" t="s">
-        <v>12</v>
-      </c>
-      <c r="I14" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -2105,28 +2206,25 @@
         <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E15" t="s">
-        <v>53</v>
-      </c>
-      <c r="F15" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="G15" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H15" t="s">
+        <v>369</v>
+      </c>
+      <c r="I15" t="s">
+        <v>50</v>
+      </c>
+      <c r="J15" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="I15" t="s">
-        <v>54</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -2137,25 +2235,22 @@
         <v>121</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
       </c>
-      <c r="F16" t="s">
-        <v>7</v>
-      </c>
       <c r="G16" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H16" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I16" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -2166,28 +2261,25 @@
         <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D17" t="s">
-        <v>252</v>
+        <v>233</v>
       </c>
       <c r="E17" t="s">
-        <v>21</v>
-      </c>
-      <c r="F17" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G17" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H17" t="s">
-        <v>51</v>
+        <v>369</v>
       </c>
       <c r="I17" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -2198,28 +2290,25 @@
         <v>424</v>
       </c>
       <c r="C18" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D18" t="s">
-        <v>252</v>
+        <v>233</v>
       </c>
       <c r="E18" t="s">
-        <v>21</v>
-      </c>
-      <c r="F18" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G18" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H18" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I18" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -2230,28 +2319,25 @@
         <v>567</v>
       </c>
       <c r="C19" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D19" t="s">
-        <v>252</v>
+        <v>233</v>
       </c>
       <c r="E19" t="s">
-        <v>21</v>
-      </c>
-      <c r="F19" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G19" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H19" t="s">
-        <v>51</v>
+        <v>369</v>
       </c>
       <c r="I19" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -2262,28 +2348,25 @@
         <v>76</v>
       </c>
       <c r="C20" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D20" t="s">
-        <v>252</v>
+        <v>233</v>
       </c>
       <c r="E20" t="s">
-        <v>53</v>
-      </c>
-      <c r="F20" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="G20" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H20" t="s">
-        <v>51</v>
+        <v>369</v>
       </c>
       <c r="I20" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -2294,92 +2377,86 @@
         <v>239</v>
       </c>
       <c r="C21" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21" t="s">
+        <v>233</v>
+      </c>
+      <c r="E21" t="s">
+        <v>49</v>
+      </c>
+      <c r="G21" t="s">
+        <v>7</v>
+      </c>
+      <c r="H21" t="s">
+        <v>369</v>
+      </c>
+      <c r="I21" t="s">
+        <v>66</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="8">
+        <v>20</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="D21" t="s">
-        <v>252</v>
-      </c>
-      <c r="E21" t="s">
-        <v>53</v>
-      </c>
-      <c r="F21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G21" t="s">
-        <v>393</v>
-      </c>
-      <c r="H21" t="s">
-        <v>51</v>
-      </c>
-      <c r="I21" t="s">
-        <v>70</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>5</v>
-      </c>
-      <c r="B22" s="4">
-        <v>20</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="D22" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" s="8">
+        <v>5</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="J22" s="9" t="s">
         <v>73</v>
-      </c>
-      <c r="D22" t="s">
-        <v>76</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" t="s">
-        <v>7</v>
-      </c>
-      <c r="G22" t="s">
-        <v>393</v>
-      </c>
-      <c r="H22" t="s">
-        <v>12</v>
-      </c>
-      <c r="I22" t="s">
-        <v>72</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B23" s="4">
         <v>155</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D23" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E23" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G23" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H23" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I23" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -2390,28 +2467,25 @@
         <v>150</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D24" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E24" t="s">
-        <v>21</v>
-      </c>
-      <c r="F24" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G24" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H24" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I24" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -2422,28 +2496,25 @@
         <v>22</v>
       </c>
       <c r="C25" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D25" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E25" t="s">
-        <v>21</v>
-      </c>
-      <c r="F25" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G25" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H25" t="s">
-        <v>51</v>
+        <v>369</v>
       </c>
       <c r="I25" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -2454,25 +2525,22 @@
         <v>739</v>
       </c>
       <c r="C26" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D26" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E26" t="s">
-        <v>21</v>
-      </c>
-      <c r="F26" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G26" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H26" t="s">
-        <v>51</v>
+        <v>369</v>
       </c>
       <c r="I26" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -2483,28 +2551,25 @@
         <v>853</v>
       </c>
       <c r="C27" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D27" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E27" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G27" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H27" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I27" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -2515,28 +2580,25 @@
         <v>84</v>
       </c>
       <c r="C28" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D28" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E28" t="s">
-        <v>53</v>
-      </c>
-      <c r="F28" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="G28" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H28" t="s">
-        <v>51</v>
+        <v>369</v>
       </c>
       <c r="I28" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -2547,28 +2609,25 @@
         <v>704</v>
       </c>
       <c r="C29" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D29" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E29" t="s">
         <v>6</v>
       </c>
-      <c r="F29" t="s">
-        <v>7</v>
-      </c>
       <c r="G29" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H29" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I29" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -2579,28 +2638,25 @@
         <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>94</v>
+        <v>384</v>
       </c>
       <c r="D30" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E30" t="s">
-        <v>21</v>
-      </c>
-      <c r="F30" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G30" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H30" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I30" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -2611,28 +2667,25 @@
         <v>875</v>
       </c>
       <c r="C31" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D31" t="s">
+        <v>87</v>
+      </c>
+      <c r="E31" t="s">
+        <v>19</v>
+      </c>
+      <c r="G31" t="s">
+        <v>7</v>
+      </c>
+      <c r="H31" t="s">
+        <v>369</v>
+      </c>
+      <c r="I31" t="s">
+        <v>88</v>
+      </c>
+      <c r="J31" s="5" t="s">
         <v>91</v>
-      </c>
-      <c r="E31" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" t="s">
-        <v>7</v>
-      </c>
-      <c r="G31" t="s">
-        <v>393</v>
-      </c>
-      <c r="H31" t="s">
-        <v>12</v>
-      </c>
-      <c r="I31" t="s">
-        <v>92</v>
-      </c>
-      <c r="J31" s="5" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -2643,28 +2696,25 @@
         <v>33</v>
       </c>
       <c r="C32" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D32" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E32" t="s">
-        <v>21</v>
-      </c>
-      <c r="F32" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G32" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H32" t="s">
-        <v>51</v>
+        <v>369</v>
       </c>
       <c r="I32" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -2675,28 +2725,25 @@
         <v>153</v>
       </c>
       <c r="C33" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D33" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E33" t="s">
-        <v>21</v>
-      </c>
-      <c r="F33" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G33" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H33" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I33" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -2707,28 +2754,25 @@
         <v>981</v>
       </c>
       <c r="C34" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D34" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E34" t="s">
-        <v>21</v>
-      </c>
-      <c r="F34" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G34" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H34" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I34" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -2739,22 +2783,19 @@
         <v>4</v>
       </c>
       <c r="C35" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D35" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E35" t="s">
-        <v>53</v>
-      </c>
-      <c r="F35" t="s">
-        <v>7</v>
-      </c>
-      <c r="H35" t="s">
-        <v>106</v>
+        <v>49</v>
+      </c>
+      <c r="G35" t="s">
+        <v>7</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -2762,31 +2803,22 @@
         <v>5</v>
       </c>
       <c r="B36" s="4">
-        <v>206</v>
+        <v>283</v>
       </c>
       <c r="C36" t="s">
-        <v>108</v>
+        <v>417</v>
       </c>
       <c r="D36" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="E36" t="s">
         <v>6</v>
       </c>
-      <c r="F36" t="s">
-        <v>7</v>
-      </c>
       <c r="G36" t="s">
         <v>393</v>
       </c>
       <c r="H36" t="s">
-        <v>51</v>
-      </c>
-      <c r="I36" t="s">
-        <v>104</v>
-      </c>
-      <c r="J36" s="5" t="s">
-        <v>109</v>
+        <v>390</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -2794,31 +2826,22 @@
         <v>5</v>
       </c>
       <c r="B37" s="4">
-        <v>21</v>
+        <v>876</v>
       </c>
       <c r="C37" t="s">
-        <v>110</v>
+        <v>415</v>
       </c>
       <c r="D37" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E37" t="s">
         <v>6</v>
       </c>
-      <c r="F37" t="s">
-        <v>7</v>
-      </c>
       <c r="G37" t="s">
         <v>393</v>
       </c>
       <c r="H37" t="s">
-        <v>51</v>
-      </c>
-      <c r="I37" t="s">
-        <v>112</v>
-      </c>
-      <c r="J37" s="5" t="s">
-        <v>113</v>
+        <v>390</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -2826,63 +2849,57 @@
         <v>5</v>
       </c>
       <c r="B38" s="4">
-        <v>143</v>
+        <v>206</v>
       </c>
       <c r="C38" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="D38" t="s">
         <v>111</v>
       </c>
       <c r="E38" t="s">
+        <v>6</v>
+      </c>
+      <c r="G38" t="s">
+        <v>7</v>
+      </c>
+      <c r="H38" t="s">
+        <v>369</v>
+      </c>
+      <c r="I38" t="s">
+        <v>99</v>
+      </c>
+      <c r="J38" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>5</v>
+      </c>
+      <c r="B39" s="4">
         <v>21</v>
       </c>
-      <c r="F38" t="s">
-        <v>7</v>
-      </c>
-      <c r="G38" t="s">
-        <v>393</v>
-      </c>
-      <c r="H38" t="s">
-        <v>51</v>
-      </c>
-      <c r="I38" t="s">
-        <v>112</v>
-      </c>
-      <c r="J38" s="5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>5</v>
-      </c>
-      <c r="B39" s="4">
-        <v>19</v>
-      </c>
       <c r="C39" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="D39" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="E39" t="s">
-        <v>21</v>
-      </c>
-      <c r="F39" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G39" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H39" t="s">
-        <v>51</v>
+        <v>369</v>
       </c>
       <c r="I39" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -2890,60 +2907,57 @@
         <v>5</v>
       </c>
       <c r="B40" s="4">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C40" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="D40" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="E40" t="s">
-        <v>21</v>
-      </c>
-      <c r="F40" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G40" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H40" t="s">
-        <v>51</v>
+        <v>369</v>
       </c>
       <c r="I40" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+      <c r="J40" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>5</v>
       </c>
       <c r="B41" s="4">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C41" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="D41" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E41" t="s">
-        <v>21</v>
-      </c>
-      <c r="F41" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G41" t="s">
-        <v>393</v>
+        <v>373</v>
       </c>
       <c r="H41" t="s">
-        <v>12</v>
+        <v>372</v>
       </c>
       <c r="I41" t="s">
-        <v>122</v>
+        <v>418</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -2951,31 +2965,25 @@
         <v>5</v>
       </c>
       <c r="B42" s="4">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C42" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="D42" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="E42" t="s">
-        <v>6</v>
-      </c>
-      <c r="F42" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="G42" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H42" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I42" t="s">
-        <v>130</v>
-      </c>
-      <c r="J42" s="5" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -2983,31 +2991,28 @@
         <v>5</v>
       </c>
       <c r="B43" s="4">
-        <v>287</v>
+        <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="D43" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="E43" t="s">
-        <v>21</v>
-      </c>
-      <c r="F43" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G43" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H43" t="s">
-        <v>51</v>
+        <v>369</v>
       </c>
       <c r="I43" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -3015,28 +3020,28 @@
         <v>5</v>
       </c>
       <c r="B44" s="4">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C44" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="D44" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="E44" t="s">
-        <v>21</v>
-      </c>
-      <c r="F44" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G44" t="s">
-        <v>393</v>
+        <v>38</v>
       </c>
       <c r="H44" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I44" t="s">
-        <v>133</v>
+        <v>123</v>
+      </c>
+      <c r="J44" s="5" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -3044,19 +3049,28 @@
         <v>5</v>
       </c>
       <c r="B45" s="4">
-        <v>23</v>
+        <v>287</v>
+      </c>
+      <c r="C45" t="s">
+        <v>120</v>
       </c>
       <c r="D45" t="s">
+        <v>114</v>
+      </c>
+      <c r="E45" t="s">
+        <v>19</v>
+      </c>
+      <c r="G45" t="s">
+        <v>7</v>
+      </c>
+      <c r="H45" t="s">
+        <v>369</v>
+      </c>
+      <c r="I45" t="s">
+        <v>122</v>
+      </c>
+      <c r="J45" s="5" t="s">
         <v>121</v>
-      </c>
-      <c r="E45" t="s">
-        <v>53</v>
-      </c>
-      <c r="F45" t="s">
-        <v>7</v>
-      </c>
-      <c r="H45" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -3064,19 +3078,25 @@
         <v>5</v>
       </c>
       <c r="B46" s="4">
-        <v>25</v>
+        <v>146</v>
+      </c>
+      <c r="C46" t="s">
+        <v>125</v>
       </c>
       <c r="D46" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E46" t="s">
-        <v>53</v>
-      </c>
-      <c r="F46" t="s">
+        <v>19</v>
+      </c>
+      <c r="G46" t="s">
         <v>7</v>
       </c>
       <c r="H46" t="s">
-        <v>106</v>
+        <v>369</v>
+      </c>
+      <c r="I46" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -3084,28 +3104,19 @@
         <v>5</v>
       </c>
       <c r="B47" s="4">
-        <v>226</v>
+        <v>23</v>
       </c>
       <c r="C47" t="s">
-        <v>134</v>
+        <v>409</v>
       </c>
       <c r="D47" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="E47" t="s">
-        <v>6</v>
-      </c>
-      <c r="F47" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="G47" t="s">
-        <v>393</v>
-      </c>
-      <c r="H47" t="s">
-        <v>12</v>
-      </c>
-      <c r="I47" t="s">
-        <v>133</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -3113,95 +3124,78 @@
         <v>5</v>
       </c>
       <c r="B48" s="4">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="C48" t="s">
-        <v>136</v>
+        <v>416</v>
       </c>
       <c r="D48" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="E48" t="s">
+        <v>49</v>
+      </c>
+      <c r="G48" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B49" s="8">
+        <v>226</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="E49" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F48" t="s">
-        <v>40</v>
-      </c>
-      <c r="G48" t="s">
-        <v>393</v>
-      </c>
-      <c r="H48" t="s">
-        <v>12</v>
-      </c>
-      <c r="I48" t="s">
-        <v>133</v>
-      </c>
-      <c r="J48" s="5" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>5</v>
-      </c>
-      <c r="B49" s="4">
-        <v>543</v>
-      </c>
-      <c r="C49" t="s">
-        <v>137</v>
-      </c>
-      <c r="D49" t="s">
-        <v>135</v>
-      </c>
-      <c r="E49" t="s">
-        <v>6</v>
-      </c>
-      <c r="F49" t="s">
-        <v>7</v>
-      </c>
-      <c r="G49" t="s">
-        <v>393</v>
-      </c>
-      <c r="H49" t="s">
-        <v>51</v>
-      </c>
-      <c r="I49" t="s">
-        <v>142</v>
-      </c>
-      <c r="J49" s="5" t="s">
-        <v>143</v>
-      </c>
+      <c r="F49" s="8">
+        <v>5</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="I49" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="J49" s="9"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>5</v>
       </c>
       <c r="B50" s="4">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C50" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="D50" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E50" t="s">
         <v>6</v>
       </c>
-      <c r="F50" t="s">
-        <v>7</v>
-      </c>
       <c r="G50" t="s">
-        <v>393</v>
+        <v>38</v>
       </c>
       <c r="H50" t="s">
-        <v>51</v>
+        <v>369</v>
       </c>
       <c r="I50" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -3209,31 +3203,28 @@
         <v>5</v>
       </c>
       <c r="B51" s="4">
-        <v>100</v>
+        <v>543</v>
       </c>
       <c r="C51" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="D51" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E51" t="s">
         <v>6</v>
       </c>
-      <c r="F51" t="s">
-        <v>7</v>
-      </c>
       <c r="G51" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H51" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I51" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -3241,31 +3232,28 @@
         <v>5</v>
       </c>
       <c r="B52" s="4">
-        <v>572</v>
+        <v>110</v>
       </c>
       <c r="C52" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="D52" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E52" t="s">
         <v>6</v>
       </c>
-      <c r="F52" t="s">
-        <v>40</v>
-      </c>
       <c r="G52" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H52" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I52" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -3273,31 +3261,28 @@
         <v>5</v>
       </c>
       <c r="B53" s="4">
-        <v>235</v>
+        <v>100</v>
       </c>
       <c r="C53" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="D53" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E53" t="s">
-        <v>21</v>
-      </c>
-      <c r="F53" t="s">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="G53" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H53" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I53" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="J53" s="5" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -3305,31 +3290,28 @@
         <v>5</v>
       </c>
       <c r="B54" s="4">
-        <v>102</v>
+        <v>572</v>
       </c>
       <c r="C54" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="D54" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E54" t="s">
-        <v>21</v>
-      </c>
-      <c r="F54" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G54" t="s">
-        <v>393</v>
+        <v>38</v>
       </c>
       <c r="H54" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I54" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="J54" s="5" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -3337,124 +3319,119 @@
         <v>5</v>
       </c>
       <c r="B55" s="4">
+        <v>235</v>
+      </c>
+      <c r="C55" t="s">
+        <v>143</v>
+      </c>
+      <c r="D55" t="s">
+        <v>128</v>
+      </c>
+      <c r="E55" t="s">
+        <v>19</v>
+      </c>
+      <c r="G55" t="s">
+        <v>38</v>
+      </c>
+      <c r="H55" t="s">
+        <v>369</v>
+      </c>
+      <c r="I55" t="s">
+        <v>144</v>
+      </c>
+      <c r="J55" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B56" s="11">
+        <v>102</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="E56" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F56" s="11">
+        <v>3</v>
+      </c>
+      <c r="G56" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="H56" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="I56" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="J56" s="12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B57" s="11">
         <v>199</v>
       </c>
-      <c r="C55" t="s">
-        <v>155</v>
-      </c>
-      <c r="D55" t="s">
-        <v>135</v>
-      </c>
-      <c r="E55" t="s">
-        <v>21</v>
-      </c>
-      <c r="F55" t="s">
-        <v>7</v>
-      </c>
-      <c r="G55" t="s">
-        <v>393</v>
-      </c>
-      <c r="H55" t="s">
-        <v>12</v>
-      </c>
-      <c r="I55" t="s">
-        <v>151</v>
-      </c>
-      <c r="J55" s="5" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>5</v>
-      </c>
-      <c r="B56" s="4">
-        <v>1448</v>
-      </c>
-      <c r="C56" t="s">
-        <v>157</v>
-      </c>
-      <c r="D56" t="s">
-        <v>135</v>
-      </c>
-      <c r="E56" t="s">
-        <v>21</v>
-      </c>
-      <c r="F56" t="s">
-        <v>7</v>
-      </c>
-      <c r="G56" t="s">
-        <v>393</v>
-      </c>
-      <c r="H56" t="s">
-        <v>51</v>
-      </c>
-      <c r="I56" t="s">
-        <v>158</v>
-      </c>
-      <c r="J56" s="5" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>5</v>
-      </c>
-      <c r="B57" s="4">
-        <v>98</v>
-      </c>
-      <c r="C57" t="s">
-        <v>161</v>
-      </c>
-      <c r="D57" t="s">
-        <v>135</v>
-      </c>
-      <c r="E57" t="s">
-        <v>21</v>
-      </c>
-      <c r="F57" t="s">
-        <v>7</v>
-      </c>
-      <c r="G57" t="s">
-        <v>393</v>
-      </c>
-      <c r="H57" t="s">
-        <v>51</v>
-      </c>
-      <c r="I57" t="s">
-        <v>160</v>
-      </c>
+      <c r="C57" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F57" s="11">
+        <v>3</v>
+      </c>
+      <c r="G57" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="H57" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="I57" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="J57" s="12"/>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>5</v>
       </c>
       <c r="B58" s="4">
-        <v>230</v>
+        <v>1448</v>
       </c>
       <c r="C58" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="D58" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E58" t="s">
-        <v>21</v>
-      </c>
-      <c r="F58" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G58" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H58" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I58" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="J58" s="5" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
@@ -3462,31 +3439,25 @@
         <v>5</v>
       </c>
       <c r="B59" s="4">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C59" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="D59" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E59" t="s">
-        <v>21</v>
-      </c>
-      <c r="F59" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G59" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H59" t="s">
-        <v>51</v>
+        <v>369</v>
       </c>
       <c r="I59" t="s">
-        <v>168</v>
-      </c>
-      <c r="J59" s="5" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
@@ -3494,22 +3465,28 @@
         <v>5</v>
       </c>
       <c r="B60" s="4">
-        <v>124</v>
+        <v>230</v>
       </c>
       <c r="C60" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="D60" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E60" t="s">
-        <v>53</v>
-      </c>
-      <c r="F60" t="s">
+        <v>19</v>
+      </c>
+      <c r="G60" t="s">
         <v>7</v>
       </c>
       <c r="H60" t="s">
-        <v>106</v>
+        <v>369</v>
+      </c>
+      <c r="I60" t="s">
+        <v>152</v>
+      </c>
+      <c r="J60" s="5" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
@@ -3517,22 +3494,28 @@
         <v>5</v>
       </c>
       <c r="B61" s="4">
-        <v>297</v>
+        <v>105</v>
       </c>
       <c r="C61" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="D61" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E61" t="s">
-        <v>53</v>
-      </c>
-      <c r="F61" t="s">
+        <v>19</v>
+      </c>
+      <c r="G61" t="s">
         <v>7</v>
       </c>
       <c r="H61" t="s">
-        <v>106</v>
+        <v>369</v>
+      </c>
+      <c r="I61" t="s">
+        <v>160</v>
+      </c>
+      <c r="J61" s="5" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
@@ -3540,31 +3523,19 @@
         <v>5</v>
       </c>
       <c r="B62" s="4">
-        <v>208</v>
+        <v>124</v>
       </c>
       <c r="C62" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="D62" t="s">
-        <v>165</v>
+        <v>128</v>
       </c>
       <c r="E62" t="s">
-        <v>21</v>
-      </c>
-      <c r="F62" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="G62" t="s">
-        <v>393</v>
-      </c>
-      <c r="H62" t="s">
-        <v>12</v>
-      </c>
-      <c r="I62" t="s">
-        <v>168</v>
-      </c>
-      <c r="J62" s="5" t="s">
-        <v>171</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
@@ -3572,31 +3543,19 @@
         <v>5</v>
       </c>
       <c r="B63" s="4">
-        <v>211</v>
+        <v>297</v>
       </c>
       <c r="C63" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="D63" t="s">
-        <v>165</v>
+        <v>128</v>
       </c>
       <c r="E63" t="s">
-        <v>21</v>
-      </c>
-      <c r="F63" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G63" t="s">
-        <v>393</v>
-      </c>
-      <c r="H63" t="s">
-        <v>51</v>
-      </c>
-      <c r="I63" t="s">
-        <v>172</v>
-      </c>
-      <c r="J63" s="5" t="s">
-        <v>175</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
@@ -3604,19 +3563,28 @@
         <v>5</v>
       </c>
       <c r="B64" s="4">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C64" t="s">
-        <v>174</v>
+        <v>162</v>
+      </c>
+      <c r="D64" t="s">
+        <v>157</v>
       </c>
       <c r="E64" t="s">
-        <v>53</v>
-      </c>
-      <c r="F64" t="s">
+        <v>19</v>
+      </c>
+      <c r="G64" t="s">
         <v>7</v>
       </c>
       <c r="H64" t="s">
-        <v>106</v>
+        <v>369</v>
+      </c>
+      <c r="I64" t="s">
+        <v>160</v>
+      </c>
+      <c r="J64" s="5" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
@@ -3624,31 +3592,28 @@
         <v>5</v>
       </c>
       <c r="B65" s="4">
-        <v>703</v>
+        <v>211</v>
       </c>
       <c r="C65" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="D65" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="E65" t="s">
-        <v>6</v>
-      </c>
-      <c r="F65" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G65" t="s">
-        <v>393</v>
+        <v>38</v>
       </c>
       <c r="H65" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I65" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="J65" s="5" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
@@ -3656,31 +3621,16 @@
         <v>5</v>
       </c>
       <c r="B66" s="4">
-        <v>1046</v>
+        <v>212</v>
       </c>
       <c r="C66" t="s">
-        <v>180</v>
-      </c>
-      <c r="D66" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="E66" t="s">
-        <v>6</v>
-      </c>
-      <c r="F66" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="G66" t="s">
-        <v>393</v>
-      </c>
-      <c r="H66" t="s">
-        <v>12</v>
-      </c>
-      <c r="I66" t="s">
-        <v>181</v>
-      </c>
-      <c r="J66" s="5" t="s">
-        <v>182</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
@@ -3688,185 +3638,178 @@
         <v>5</v>
       </c>
       <c r="B67" s="4">
+        <v>703</v>
+      </c>
+      <c r="C67" t="s">
+        <v>168</v>
+      </c>
+      <c r="D67" t="s">
+        <v>170</v>
+      </c>
+      <c r="E67" t="s">
+        <v>6</v>
+      </c>
+      <c r="G67" t="s">
+        <v>7</v>
+      </c>
+      <c r="H67" t="s">
+        <v>369</v>
+      </c>
+      <c r="I67" t="s">
+        <v>169</v>
+      </c>
+      <c r="J67" s="5" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>5</v>
+      </c>
+      <c r="B68" s="4">
+        <v>1046</v>
+      </c>
+      <c r="C68" t="s">
+        <v>172</v>
+      </c>
+      <c r="D68" t="s">
+        <v>170</v>
+      </c>
+      <c r="E68" t="s">
+        <v>6</v>
+      </c>
+      <c r="G68" t="s">
+        <v>7</v>
+      </c>
+      <c r="H68" t="s">
+        <v>369</v>
+      </c>
+      <c r="I68" t="s">
+        <v>173</v>
+      </c>
+      <c r="J68" s="5" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B69" s="11">
         <v>973</v>
       </c>
-      <c r="C67" t="s">
-        <v>183</v>
-      </c>
-      <c r="D67" t="s">
-        <v>178</v>
-      </c>
-      <c r="E67" t="s">
-        <v>21</v>
-      </c>
-      <c r="F67" t="s">
-        <v>7</v>
-      </c>
-      <c r="G67" t="s">
+      <c r="C69" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D69" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="E69" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F69" s="11">
+        <v>3</v>
+      </c>
+      <c r="G69" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="H69" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="I69" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="J69" s="12" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" s="7" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B70" s="8">
+        <v>215</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F70" s="8">
+        <v>5</v>
+      </c>
+      <c r="G70" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="H70" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="I70" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="J70" s="9" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>5</v>
+      </c>
+      <c r="B71" s="4">
+        <v>378</v>
+      </c>
+      <c r="C71" t="s">
+        <v>413</v>
+      </c>
+      <c r="D71" t="s">
+        <v>170</v>
+      </c>
+      <c r="E71" t="s">
+        <v>19</v>
+      </c>
+      <c r="F71"/>
+      <c r="G71" t="s">
         <v>393</v>
       </c>
-      <c r="H67" t="s">
-        <v>12</v>
-      </c>
-      <c r="I67" t="s">
-        <v>181</v>
-      </c>
-      <c r="J67" s="5" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>5</v>
-      </c>
-      <c r="B68" s="4">
-        <v>215</v>
-      </c>
-      <c r="C68" t="s">
-        <v>185</v>
-      </c>
-      <c r="D68" t="s">
-        <v>178</v>
-      </c>
-      <c r="E68" t="s">
-        <v>21</v>
-      </c>
-      <c r="F68" t="s">
-        <v>7</v>
-      </c>
-      <c r="G68" t="s">
-        <v>393</v>
-      </c>
-      <c r="H68" t="s">
-        <v>12</v>
-      </c>
-      <c r="I68" t="s">
-        <v>186</v>
-      </c>
-      <c r="J68" s="5" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>5</v>
-      </c>
-      <c r="B69" s="4">
-        <v>621</v>
-      </c>
-      <c r="C69" t="s">
-        <v>188</v>
-      </c>
-      <c r="D69" t="s">
-        <v>178</v>
-      </c>
-      <c r="E69" t="s">
-        <v>21</v>
-      </c>
-      <c r="F69" t="s">
-        <v>7</v>
-      </c>
-      <c r="G69" t="s">
-        <v>393</v>
-      </c>
-      <c r="H69" t="s">
-        <v>12</v>
-      </c>
-      <c r="I69" t="s">
-        <v>191</v>
-      </c>
-      <c r="J69" s="5" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>5</v>
-      </c>
-      <c r="B70" s="4">
-        <v>355</v>
-      </c>
-      <c r="C70" t="s">
-        <v>190</v>
-      </c>
-      <c r="D70" t="s">
-        <v>178</v>
-      </c>
-      <c r="E70" t="s">
-        <v>21</v>
-      </c>
-      <c r="F70" t="s">
-        <v>7</v>
-      </c>
-      <c r="G70" t="s">
-        <v>393</v>
-      </c>
-      <c r="H70" t="s">
-        <v>12</v>
-      </c>
-      <c r="I70" t="s">
-        <v>195</v>
-      </c>
-      <c r="J70" s="5" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>5</v>
-      </c>
-      <c r="B71" s="4">
-        <v>295</v>
-      </c>
-      <c r="C71" t="s">
-        <v>192</v>
-      </c>
-      <c r="D71" t="s">
-        <v>178</v>
-      </c>
-      <c r="E71" t="s">
-        <v>53</v>
-      </c>
-      <c r="F71" t="s">
-        <v>7</v>
-      </c>
       <c r="H71" t="s">
-        <v>106</v>
-      </c>
-      <c r="J71" s="5" t="s">
-        <v>193</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="I71" t="s">
+        <v>411</v>
+      </c>
+      <c r="J71"/>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>5</v>
       </c>
       <c r="B72" s="4">
-        <v>76</v>
+        <v>621</v>
       </c>
       <c r="C72" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
       <c r="D72" t="s">
-        <v>194</v>
+        <v>170</v>
       </c>
       <c r="E72" t="s">
-        <v>21</v>
-      </c>
-      <c r="F72" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G72" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H72" t="s">
-        <v>51</v>
+        <v>369</v>
       </c>
       <c r="I72" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="J72" s="5" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
@@ -3874,63 +3817,60 @@
         <v>5</v>
       </c>
       <c r="B73" s="4">
-        <v>39</v>
+        <v>355</v>
       </c>
       <c r="C73" t="s">
-        <v>201</v>
+        <v>179</v>
       </c>
       <c r="D73" t="s">
-        <v>194</v>
+        <v>170</v>
       </c>
       <c r="E73" t="s">
-        <v>21</v>
-      </c>
-      <c r="F73" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="G73" t="s">
+        <v>7</v>
+      </c>
+      <c r="H73" t="s">
+        <v>369</v>
+      </c>
+      <c r="I73" t="s">
+        <v>184</v>
+      </c>
+      <c r="J73" s="5" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B74" s="11">
+        <v>23</v>
+      </c>
+      <c r="C74" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="D74" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="E74" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F74" s="11">
+        <v>2</v>
+      </c>
+      <c r="G74" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="H73" t="s">
-        <v>51</v>
-      </c>
-      <c r="I73" t="s">
-        <v>195</v>
-      </c>
-      <c r="J73" s="5" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>5</v>
-      </c>
-      <c r="B74" s="4">
-        <v>46</v>
-      </c>
-      <c r="C74" t="s">
-        <v>203</v>
-      </c>
-      <c r="D74" t="s">
-        <v>194</v>
-      </c>
-      <c r="E74" t="s">
-        <v>21</v>
-      </c>
-      <c r="F74" t="s">
-        <v>7</v>
-      </c>
-      <c r="G74" t="s">
-        <v>393</v>
-      </c>
-      <c r="H74" t="s">
-        <v>51</v>
-      </c>
-      <c r="I74" t="s">
-        <v>204</v>
-      </c>
-      <c r="J74" s="5" t="s">
-        <v>205</v>
+      <c r="H74" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="I74" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="J74" s="12" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
@@ -3938,92 +3878,86 @@
         <v>5</v>
       </c>
       <c r="B75" s="4">
-        <v>90</v>
+        <v>295</v>
       </c>
       <c r="C75" t="s">
-        <v>206</v>
+        <v>181</v>
       </c>
       <c r="D75" t="s">
-        <v>194</v>
+        <v>170</v>
       </c>
       <c r="E75" t="s">
-        <v>21</v>
-      </c>
-      <c r="F75" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="G75" t="s">
-        <v>393</v>
-      </c>
-      <c r="H75" t="s">
-        <v>12</v>
-      </c>
-      <c r="I75" t="s">
-        <v>204</v>
+        <v>7</v>
       </c>
       <c r="J75" s="5" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>5</v>
-      </c>
-      <c r="B76" s="4">
-        <v>40</v>
-      </c>
-      <c r="C76" t="s">
-        <v>208</v>
-      </c>
-      <c r="D76" t="s">
-        <v>194</v>
-      </c>
-      <c r="E76" t="s">
-        <v>21</v>
-      </c>
-      <c r="F76" t="s">
-        <v>7</v>
-      </c>
-      <c r="G76" t="s">
-        <v>393</v>
-      </c>
-      <c r="H76" t="s">
-        <v>12</v>
-      </c>
-      <c r="I76" t="s">
-        <v>209</v>
-      </c>
-      <c r="J76" s="5" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>5</v>
-      </c>
-      <c r="B77" s="4">
-        <v>79</v>
-      </c>
-      <c r="C77" t="s">
-        <v>211</v>
-      </c>
-      <c r="D77" t="s">
-        <v>194</v>
-      </c>
-      <c r="E77" t="s">
-        <v>21</v>
-      </c>
-      <c r="F77" t="s">
-        <v>7</v>
-      </c>
-      <c r="G77" t="s">
-        <v>393</v>
-      </c>
-      <c r="H77" t="s">
-        <v>12</v>
-      </c>
-      <c r="I77" t="s">
-        <v>209</v>
+        <v>182</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B76" s="11">
+        <v>76</v>
+      </c>
+      <c r="C76" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="D76" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F76" s="11">
+        <v>3</v>
+      </c>
+      <c r="G76" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="H76" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="I76" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="J76" s="12" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B77" s="11">
+        <v>39</v>
+      </c>
+      <c r="C77" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="D77" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="E77" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F77" s="11">
+        <v>3</v>
+      </c>
+      <c r="G77" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="H77" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="I77" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="J77" s="12" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
@@ -4031,31 +3965,28 @@
         <v>5</v>
       </c>
       <c r="B78" s="4">
-        <v>131</v>
+        <v>46</v>
       </c>
       <c r="C78" t="s">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="D78" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="E78" t="s">
-        <v>21</v>
-      </c>
-      <c r="F78" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G78" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H78" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I78" t="s">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="J78" s="5" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
@@ -4063,31 +3994,28 @@
         <v>5</v>
       </c>
       <c r="B79" s="4">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="C79" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
       <c r="D79" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="E79" t="s">
-        <v>21</v>
-      </c>
-      <c r="F79" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G79" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H79" t="s">
-        <v>51</v>
+        <v>369</v>
       </c>
       <c r="I79" t="s">
-        <v>226</v>
+        <v>192</v>
       </c>
       <c r="J79" s="5" t="s">
-        <v>227</v>
+        <v>195</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
@@ -4095,22 +4023,28 @@
         <v>5</v>
       </c>
       <c r="B80" s="4">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C80" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="D80" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="E80" t="s">
-        <v>53</v>
-      </c>
-      <c r="F80" t="s">
+        <v>19</v>
+      </c>
+      <c r="G80" t="s">
         <v>7</v>
       </c>
       <c r="H80" t="s">
-        <v>106</v>
+        <v>369</v>
+      </c>
+      <c r="I80" t="s">
+        <v>197</v>
+      </c>
+      <c r="J80" s="5" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
@@ -4118,159 +4052,139 @@
         <v>5</v>
       </c>
       <c r="B81" s="4">
+        <v>79</v>
+      </c>
+      <c r="C81" t="s">
+        <v>199</v>
+      </c>
+      <c r="D81" t="s">
+        <v>183</v>
+      </c>
+      <c r="E81" t="s">
+        <v>19</v>
+      </c>
+      <c r="G81" t="s">
+        <v>7</v>
+      </c>
+      <c r="H81" t="s">
+        <v>369</v>
+      </c>
+      <c r="I81" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B82" s="11">
+        <v>131</v>
+      </c>
+      <c r="C82" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="C81" t="s">
-        <v>217</v>
-      </c>
-      <c r="D81" t="s">
-        <v>218</v>
-      </c>
-      <c r="E81" t="s">
-        <v>21</v>
-      </c>
-      <c r="F81" t="s">
-        <v>7</v>
-      </c>
-      <c r="G81" t="s">
-        <v>393</v>
-      </c>
-      <c r="H81" t="s">
-        <v>12</v>
-      </c>
-      <c r="I81" t="s">
-        <v>228</v>
-      </c>
-      <c r="J81" s="5" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>5</v>
-      </c>
-      <c r="B82" s="4">
-        <v>133</v>
-      </c>
-      <c r="C82" t="s">
-        <v>222</v>
-      </c>
-      <c r="D82" t="s">
-        <v>218</v>
-      </c>
-      <c r="E82" t="s">
-        <v>21</v>
-      </c>
-      <c r="F82" t="s">
-        <v>7</v>
-      </c>
-      <c r="G82" t="s">
-        <v>393</v>
-      </c>
-      <c r="H82" t="s">
-        <v>12</v>
-      </c>
-      <c r="I82" t="s">
-        <v>230</v>
-      </c>
-      <c r="J82" s="5" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>5</v>
-      </c>
-      <c r="B83" s="4">
-        <v>695</v>
-      </c>
-      <c r="C83" t="s">
-        <v>223</v>
-      </c>
-      <c r="D83" t="s">
-        <v>218</v>
-      </c>
-      <c r="E83" t="s">
-        <v>21</v>
-      </c>
-      <c r="F83" t="s">
-        <v>7</v>
-      </c>
-      <c r="G83" t="s">
-        <v>393</v>
-      </c>
-      <c r="H83" t="s">
-        <v>12</v>
-      </c>
-      <c r="I83" t="s">
-        <v>230</v>
-      </c>
-      <c r="J83" s="5" t="s">
-        <v>232</v>
-      </c>
+      <c r="D82" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="E82" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F82" s="11">
+        <v>2</v>
+      </c>
+      <c r="G82" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H82" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="I82" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="J82" s="12" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B83" s="11">
+        <v>17</v>
+      </c>
+      <c r="C83" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="D83" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="E83" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F83" s="11">
+        <v>3</v>
+      </c>
+      <c r="G83" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="H83" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="I83" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="J83" s="12"/>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>5</v>
       </c>
       <c r="B84" s="4">
-        <v>417</v>
+        <v>51</v>
       </c>
       <c r="C84" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="D84" t="s">
-        <v>218</v>
+        <v>183</v>
       </c>
       <c r="E84" t="s">
-        <v>21</v>
-      </c>
-      <c r="F84" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="G84" t="s">
-        <v>393</v>
-      </c>
-      <c r="H84" t="s">
-        <v>51</v>
-      </c>
-      <c r="I84" t="s">
-        <v>233</v>
-      </c>
-      <c r="J84" s="5" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>5</v>
-      </c>
-      <c r="B85" s="4">
-        <v>130</v>
-      </c>
-      <c r="C85" t="s">
-        <v>225</v>
-      </c>
-      <c r="D85" t="s">
-        <v>218</v>
-      </c>
-      <c r="E85" t="s">
-        <v>21</v>
-      </c>
-      <c r="F85" t="s">
-        <v>7</v>
-      </c>
-      <c r="G85" t="s">
-        <v>393</v>
-      </c>
-      <c r="H85" t="s">
-        <v>12</v>
-      </c>
-      <c r="I85" t="s">
-        <v>234</v>
-      </c>
-      <c r="J85" s="5" t="s">
-        <v>235</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B85" s="11">
+        <v>200</v>
+      </c>
+      <c r="C85" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="D85" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="E85" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F85" s="11">
+        <v>3</v>
+      </c>
+      <c r="G85" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="H85" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="I85" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="J85" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
@@ -4278,28 +4192,28 @@
         <v>5</v>
       </c>
       <c r="B86" s="4">
-        <v>994</v>
+        <v>133</v>
       </c>
       <c r="C86" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="D86" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="E86" t="s">
-        <v>21</v>
-      </c>
-      <c r="F86" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G86" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H86" t="s">
-        <v>51</v>
+        <v>369</v>
       </c>
       <c r="I86" t="s">
-        <v>236</v>
+        <v>214</v>
+      </c>
+      <c r="J86" s="5" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
@@ -4307,31 +4221,28 @@
         <v>5</v>
       </c>
       <c r="B87" s="4">
-        <v>286</v>
+        <v>695</v>
       </c>
       <c r="C87" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="D87" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="E87" t="s">
-        <v>21</v>
-      </c>
-      <c r="F87" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G87" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H87" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I87" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="J87" s="5" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
@@ -4339,31 +4250,28 @@
         <v>5</v>
       </c>
       <c r="B88" s="4">
-        <v>207</v>
+        <v>417</v>
       </c>
       <c r="C88" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="D88" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="E88" t="s">
-        <v>21</v>
-      </c>
-      <c r="F88" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G88" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H88" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I88" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="J88" s="5" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
@@ -4371,31 +4279,28 @@
         <v>5</v>
       </c>
       <c r="B89" s="4">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="C89" t="s">
-        <v>239</v>
+        <v>212</v>
       </c>
       <c r="D89" t="s">
+        <v>205</v>
+      </c>
+      <c r="E89" t="s">
+        <v>19</v>
+      </c>
+      <c r="G89" t="s">
+        <v>7</v>
+      </c>
+      <c r="H89" t="s">
+        <v>369</v>
+      </c>
+      <c r="I89" t="s">
         <v>218</v>
       </c>
-      <c r="E89" t="s">
-        <v>21</v>
-      </c>
-      <c r="F89" t="s">
-        <v>7</v>
-      </c>
-      <c r="G89" t="s">
-        <v>393</v>
-      </c>
-      <c r="H89" t="s">
-        <v>12</v>
-      </c>
-      <c r="I89" t="s">
-        <v>242</v>
-      </c>
       <c r="J89" s="5" t="s">
-        <v>374</v>
+        <v>219</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
@@ -4403,95 +4308,89 @@
         <v>5</v>
       </c>
       <c r="B90" s="4">
-        <v>684</v>
+        <v>994</v>
       </c>
       <c r="C90" t="s">
-        <v>240</v>
+        <v>206</v>
       </c>
       <c r="D90" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="E90" t="s">
-        <v>21</v>
-      </c>
-      <c r="F90" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G90" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H90" t="s">
-        <v>51</v>
+        <v>369</v>
       </c>
       <c r="I90" t="s">
-        <v>242</v>
-      </c>
-      <c r="J90" s="5" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>5</v>
-      </c>
-      <c r="B91" s="4">
-        <v>323</v>
-      </c>
-      <c r="C91" t="s">
-        <v>241</v>
-      </c>
-      <c r="D91" t="s">
-        <v>218</v>
-      </c>
-      <c r="E91" t="s">
-        <v>21</v>
-      </c>
-      <c r="F91" t="s">
-        <v>40</v>
-      </c>
-      <c r="G91" t="s">
-        <v>393</v>
-      </c>
-      <c r="H91" t="s">
-        <v>51</v>
-      </c>
-      <c r="I91" t="s">
-        <v>245</v>
-      </c>
-      <c r="J91" s="5" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>348</v>
-      </c>
-      <c r="B92" s="4">
-        <v>261</v>
-      </c>
-      <c r="C92" t="s">
-        <v>249</v>
-      </c>
-      <c r="D92" t="s">
-        <v>218</v>
-      </c>
-      <c r="E92" t="s">
-        <v>21</v>
-      </c>
-      <c r="F92" t="s">
-        <v>40</v>
-      </c>
-      <c r="G92" t="s">
-        <v>393</v>
-      </c>
-      <c r="H92" t="s">
-        <v>51</v>
-      </c>
-      <c r="I92" t="s">
-        <v>250</v>
-      </c>
-      <c r="J92" s="5" t="s">
-        <v>251</v>
+        <v>220</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A91" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B91" s="11">
+        <v>286</v>
+      </c>
+      <c r="C91" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="D91" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="E91" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F91" s="11">
+        <v>3</v>
+      </c>
+      <c r="G91" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="H91" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="I91" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="J91" s="12" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B92" s="11">
+        <v>207</v>
+      </c>
+      <c r="C92" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="D92" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="E92" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F92" s="11">
+        <v>3</v>
+      </c>
+      <c r="G92" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="H92" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="I92" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="J92" s="12" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
@@ -4499,22 +4398,28 @@
         <v>5</v>
       </c>
       <c r="B93" s="4">
-        <v>127</v>
+        <v>210</v>
       </c>
       <c r="C93" t="s">
-        <v>253</v>
+        <v>221</v>
       </c>
       <c r="D93" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="E93" t="s">
-        <v>53</v>
-      </c>
-      <c r="F93" t="s">
+        <v>19</v>
+      </c>
+      <c r="G93" t="s">
         <v>7</v>
       </c>
       <c r="H93" t="s">
-        <v>106</v>
+        <v>369</v>
+      </c>
+      <c r="I93" t="s">
+        <v>224</v>
+      </c>
+      <c r="J93" s="5" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
@@ -4522,109 +4427,118 @@
         <v>5</v>
       </c>
       <c r="B94" s="4">
-        <v>332</v>
+        <v>684</v>
       </c>
       <c r="C94" t="s">
-        <v>254</v>
+        <v>222</v>
       </c>
       <c r="D94" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="E94" t="s">
-        <v>53</v>
-      </c>
-      <c r="F94" t="s">
+        <v>19</v>
+      </c>
+      <c r="G94" t="s">
         <v>7</v>
       </c>
       <c r="H94" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>369</v>
+      </c>
+      <c r="I94" t="s">
+        <v>224</v>
+      </c>
+      <c r="J94" s="5" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>5</v>
       </c>
       <c r="B95" s="4">
-        <v>1584</v>
+        <v>323</v>
       </c>
       <c r="C95" t="s">
-        <v>256</v>
+        <v>223</v>
       </c>
       <c r="D95" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="E95" t="s">
-        <v>21</v>
-      </c>
-      <c r="F95" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G95" t="s">
-        <v>393</v>
+        <v>38</v>
       </c>
       <c r="H95" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I95" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="J95" s="5" t="s">
-        <v>258</v>
+        <v>229</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>5</v>
+        <v>324</v>
       </c>
       <c r="B96" s="4">
-        <v>743</v>
+        <v>261</v>
       </c>
       <c r="C96" t="s">
-        <v>259</v>
+        <v>230</v>
       </c>
       <c r="D96" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="E96" t="s">
-        <v>21</v>
-      </c>
-      <c r="F96" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G96" t="s">
-        <v>393</v>
+        <v>38</v>
       </c>
       <c r="H96" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I96" t="s">
-        <v>261</v>
+        <v>231</v>
       </c>
       <c r="J96" s="5" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>5</v>
-      </c>
-      <c r="B97" s="4">
-        <v>778</v>
-      </c>
-      <c r="C97" t="s">
-        <v>262</v>
-      </c>
-      <c r="D97" t="s">
-        <v>218</v>
-      </c>
-      <c r="E97" t="s">
-        <v>53</v>
-      </c>
-      <c r="F97" t="s">
-        <v>7</v>
-      </c>
-      <c r="H97" t="s">
-        <v>106</v>
+        <v>232</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B97" s="11">
+        <v>127</v>
+      </c>
+      <c r="C97" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="D97" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="E97" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F97" s="11">
+        <v>3</v>
+      </c>
+      <c r="G97" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="H97" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="I97" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="J97" s="12" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
@@ -4632,22 +4546,19 @@
         <v>5</v>
       </c>
       <c r="B98" s="4">
-        <v>269</v>
+        <v>332</v>
       </c>
       <c r="C98" t="s">
-        <v>263</v>
+        <v>235</v>
       </c>
       <c r="D98" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="E98" t="s">
-        <v>53</v>
-      </c>
-      <c r="F98" t="s">
-        <v>7</v>
-      </c>
-      <c r="H98" t="s">
-        <v>106</v>
+        <v>49</v>
+      </c>
+      <c r="G98" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="99" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -4655,31 +4566,28 @@
         <v>5</v>
       </c>
       <c r="B99" s="4">
-        <v>787</v>
+        <v>1584</v>
       </c>
       <c r="C99" t="s">
-        <v>264</v>
+        <v>237</v>
       </c>
       <c r="D99" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="E99" t="s">
-        <v>21</v>
-      </c>
-      <c r="F99" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G99" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H99" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I99" t="s">
-        <v>265</v>
+        <v>238</v>
       </c>
       <c r="J99" s="5" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
@@ -4687,31 +4595,28 @@
         <v>5</v>
       </c>
       <c r="B100" s="4">
-        <v>70</v>
+        <v>743</v>
       </c>
       <c r="C100" t="s">
-        <v>268</v>
+        <v>240</v>
       </c>
       <c r="D100" t="s">
-        <v>269</v>
+        <v>205</v>
       </c>
       <c r="E100" t="s">
-        <v>6</v>
-      </c>
-      <c r="F100" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="G100" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H100" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I100" t="s">
-        <v>270</v>
+        <v>242</v>
       </c>
       <c r="J100" s="5" t="s">
-        <v>274</v>
+        <v>241</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
@@ -4719,31 +4624,19 @@
         <v>5</v>
       </c>
       <c r="B101" s="4">
-        <v>746</v>
+        <v>778</v>
       </c>
       <c r="C101" t="s">
-        <v>271</v>
+        <v>243</v>
       </c>
       <c r="D101" t="s">
-        <v>269</v>
+        <v>205</v>
       </c>
       <c r="E101" t="s">
-        <v>6</v>
-      </c>
-      <c r="F101" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="G101" t="s">
-        <v>393</v>
-      </c>
-      <c r="H101" t="s">
-        <v>12</v>
-      </c>
-      <c r="I101" t="s">
-        <v>272</v>
-      </c>
-      <c r="J101" s="5" t="s">
-        <v>273</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
@@ -4751,220 +4644,211 @@
         <v>5</v>
       </c>
       <c r="B102" s="4">
-        <v>198</v>
+        <v>269</v>
       </c>
       <c r="C102" t="s">
-        <v>275</v>
+        <v>244</v>
       </c>
       <c r="D102" t="s">
-        <v>269</v>
+        <v>205</v>
       </c>
       <c r="E102" t="s">
-        <v>21</v>
-      </c>
-      <c r="F102" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="G102" t="s">
+        <v>373</v>
+      </c>
+      <c r="H102" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>5</v>
+      </c>
+      <c r="B103" s="4">
+        <v>787</v>
+      </c>
+      <c r="C103" t="s">
+        <v>245</v>
+      </c>
+      <c r="D103" t="s">
+        <v>205</v>
+      </c>
+      <c r="E103" t="s">
+        <v>19</v>
+      </c>
+      <c r="G103" t="s">
+        <v>7</v>
+      </c>
+      <c r="H103" t="s">
+        <v>369</v>
+      </c>
+      <c r="I103" t="s">
+        <v>246</v>
+      </c>
+      <c r="J103" s="5" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B104" s="11">
+        <v>725</v>
+      </c>
+      <c r="C104" s="10" t="s">
+        <v>389</v>
+      </c>
+      <c r="D104" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="E104" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F104" s="11">
+        <v>2</v>
+      </c>
+      <c r="G104" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="H102" t="s">
-        <v>12</v>
-      </c>
-      <c r="I102" t="s">
-        <v>272</v>
-      </c>
-      <c r="J102" s="5" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>5</v>
-      </c>
-      <c r="B103" s="4">
-        <v>213</v>
-      </c>
-      <c r="C103" t="s">
-        <v>276</v>
-      </c>
-      <c r="D103" t="s">
-        <v>269</v>
-      </c>
-      <c r="E103" t="s">
-        <v>21</v>
-      </c>
-      <c r="F103" t="s">
-        <v>7</v>
-      </c>
-      <c r="G103" t="s">
+      <c r="H104" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="I104" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="J104" s="12" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A105" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B105" s="11">
+        <v>773</v>
+      </c>
+      <c r="C105" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="D105" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="E105" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F105" s="11">
+        <v>2</v>
+      </c>
+      <c r="G105" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="H103" t="s">
-        <v>51</v>
-      </c>
-      <c r="I103" t="s">
-        <v>283</v>
-      </c>
-      <c r="J103" s="5" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>5</v>
-      </c>
-      <c r="B104" s="4">
-        <v>5</v>
-      </c>
-      <c r="C104" t="s">
-        <v>280</v>
-      </c>
-      <c r="D104" t="s">
-        <v>269</v>
-      </c>
-      <c r="E104" t="s">
-        <v>21</v>
-      </c>
-      <c r="F104" t="s">
-        <v>40</v>
-      </c>
-      <c r="G104" t="s">
+      <c r="H105" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="I105" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="J105" s="12" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B106" s="11">
+        <v>444</v>
+      </c>
+      <c r="C106" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="D106" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="E106" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F106" s="11">
+        <v>2</v>
+      </c>
+      <c r="G106" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="H104" t="s">
-        <v>12</v>
-      </c>
-      <c r="I104" t="s">
-        <v>283</v>
-      </c>
-      <c r="J104" s="5" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>5</v>
-      </c>
-      <c r="B105" s="4">
-        <v>647</v>
-      </c>
-      <c r="C105" t="s">
-        <v>282</v>
-      </c>
-      <c r="D105" t="s">
-        <v>269</v>
-      </c>
-      <c r="E105" t="s">
-        <v>21</v>
-      </c>
-      <c r="F105" t="s">
-        <v>40</v>
-      </c>
-      <c r="G105" t="s">
+      <c r="H106" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="I106" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="J106" s="12" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="B107" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C107" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="D107" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="E107" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F107" s="11">
+        <v>3</v>
+      </c>
+      <c r="G107" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="H105" t="s">
-        <v>51</v>
-      </c>
-      <c r="I105" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>5</v>
-      </c>
-      <c r="B106" s="4">
-        <v>91</v>
-      </c>
-      <c r="C106" t="s">
-        <v>284</v>
-      </c>
-      <c r="D106" t="s">
-        <v>269</v>
-      </c>
-      <c r="E106" t="s">
-        <v>21</v>
-      </c>
-      <c r="F106" t="s">
-        <v>7</v>
-      </c>
-      <c r="G106" t="s">
+      <c r="H107" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="I107" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="J107" s="12" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="B108" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C108" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="D108" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="E108" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F108" s="11">
+        <v>2</v>
+      </c>
+      <c r="G108" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="H106" t="s">
-        <v>51</v>
-      </c>
-      <c r="I106" t="s">
-        <v>285</v>
-      </c>
-      <c r="J106" s="5" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>5</v>
-      </c>
-      <c r="B107" s="4">
-        <v>322</v>
-      </c>
-      <c r="C107" t="s">
-        <v>286</v>
-      </c>
-      <c r="D107" t="s">
-        <v>269</v>
-      </c>
-      <c r="E107" t="s">
-        <v>21</v>
-      </c>
-      <c r="F107" t="s">
-        <v>7</v>
-      </c>
-      <c r="G107" t="s">
-        <v>393</v>
-      </c>
-      <c r="H107" t="s">
-        <v>51</v>
-      </c>
-      <c r="I107" t="s">
-        <v>287</v>
-      </c>
-      <c r="J107" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>5</v>
-      </c>
-      <c r="B108" s="4">
-        <v>152</v>
-      </c>
-      <c r="C108" t="s">
-        <v>290</v>
-      </c>
-      <c r="D108" t="s">
-        <v>269</v>
-      </c>
-      <c r="E108" t="s">
-        <v>21</v>
-      </c>
-      <c r="F108" t="s">
-        <v>7</v>
-      </c>
-      <c r="G108" t="s">
-        <v>393</v>
-      </c>
-      <c r="H108" t="s">
-        <v>51</v>
-      </c>
-      <c r="I108" t="s">
-        <v>291</v>
-      </c>
-      <c r="J108" s="5" t="s">
-        <v>292</v>
+      <c r="H108" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="I108" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="J108" s="12" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
@@ -4972,121 +4856,111 @@
         <v>5</v>
       </c>
       <c r="B109" s="4">
-        <v>139</v>
+        <v>547</v>
       </c>
       <c r="C109" t="s">
-        <v>293</v>
+        <v>227</v>
       </c>
       <c r="D109" t="s">
-        <v>269</v>
+        <v>228</v>
       </c>
       <c r="E109" t="s">
-        <v>21</v>
-      </c>
-      <c r="F109" t="s">
-        <v>7</v>
-      </c>
-      <c r="G109" t="s">
-        <v>393</v>
-      </c>
-      <c r="H109" t="s">
-        <v>12</v>
-      </c>
-      <c r="I109" t="s">
-        <v>294</v>
-      </c>
-      <c r="J109" s="5" t="s">
-        <v>295</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="F109"/>
+      <c r="J109"/>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>5</v>
       </c>
       <c r="B110" s="4">
-        <v>300</v>
+        <v>70</v>
       </c>
       <c r="C110" t="s">
-        <v>296</v>
+        <v>249</v>
       </c>
       <c r="D110" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="E110" t="s">
-        <v>21</v>
-      </c>
-      <c r="F110" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G110" t="s">
-        <v>393</v>
+        <v>38</v>
       </c>
       <c r="H110" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I110" t="s">
-        <v>294</v>
+        <v>251</v>
       </c>
       <c r="J110" s="5" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>5</v>
-      </c>
-      <c r="B111" s="4">
-        <v>416</v>
-      </c>
-      <c r="C111" t="s">
-        <v>297</v>
-      </c>
-      <c r="D111" t="s">
-        <v>269</v>
-      </c>
-      <c r="E111" t="s">
-        <v>21</v>
-      </c>
-      <c r="F111" t="s">
-        <v>7</v>
-      </c>
-      <c r="G111" t="s">
-        <v>393</v>
-      </c>
-      <c r="H111" t="s">
-        <v>12</v>
-      </c>
-      <c r="I111" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>5</v>
-      </c>
-      <c r="B112" s="4">
-        <v>62</v>
-      </c>
-      <c r="C112" t="s">
-        <v>298</v>
-      </c>
-      <c r="D112" t="s">
-        <v>269</v>
-      </c>
-      <c r="E112" t="s">
-        <v>21</v>
-      </c>
-      <c r="F112" t="s">
-        <v>7</v>
-      </c>
-      <c r="G112" t="s">
-        <v>393</v>
-      </c>
-      <c r="H112" t="s">
-        <v>12</v>
-      </c>
-      <c r="I112" t="s">
-        <v>303</v>
+        <v>254</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B111" s="11">
+        <v>746</v>
+      </c>
+      <c r="C111" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="D111" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="E111" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F111" s="11">
+        <v>3</v>
+      </c>
+      <c r="G111" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="H111" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="I111" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="J111" s="12" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B112" s="11">
+        <v>198</v>
+      </c>
+      <c r="C112" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="D112" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="E112" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F112" s="11">
+        <v>3</v>
+      </c>
+      <c r="G112" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="H112" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="I112" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="J112" s="12" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
@@ -5094,28 +4968,28 @@
         <v>5</v>
       </c>
       <c r="B113" s="4">
-        <v>1143</v>
+        <v>213</v>
       </c>
       <c r="C113" t="s">
-        <v>299</v>
+        <v>256</v>
       </c>
       <c r="D113" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="E113" t="s">
-        <v>21</v>
-      </c>
-      <c r="F113" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G113" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H113" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I113" t="s">
-        <v>304</v>
+        <v>263</v>
+      </c>
+      <c r="J113" s="5" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
@@ -5123,31 +4997,28 @@
         <v>5</v>
       </c>
       <c r="B114" s="4">
-        <v>309</v>
+        <v>5</v>
       </c>
       <c r="C114" t="s">
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="D114" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="E114" t="s">
-        <v>21</v>
-      </c>
-      <c r="F114" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G114" t="s">
-        <v>393</v>
+        <v>38</v>
       </c>
       <c r="H114" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I114" t="s">
-        <v>318</v>
+        <v>263</v>
       </c>
       <c r="J114" s="5" t="s">
-        <v>313</v>
+        <v>261</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
@@ -5155,95 +5026,89 @@
         <v>5</v>
       </c>
       <c r="B115" s="4">
-        <v>518</v>
+        <v>647</v>
       </c>
       <c r="C115" t="s">
-        <v>305</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="E115" t="s">
-        <v>21</v>
-      </c>
-      <c r="F115" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G115" t="s">
-        <v>393</v>
+        <v>38</v>
       </c>
       <c r="H115" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I115" t="s">
-        <v>317</v>
-      </c>
-      <c r="J115" s="5" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>5</v>
-      </c>
-      <c r="B116" s="4">
-        <v>494</v>
-      </c>
-      <c r="C116" t="s">
-        <v>306</v>
-      </c>
-      <c r="D116" t="s">
-        <v>269</v>
-      </c>
-      <c r="E116" t="s">
-        <v>21</v>
-      </c>
-      <c r="F116" t="s">
-        <v>7</v>
-      </c>
-      <c r="G116" t="s">
-        <v>393</v>
-      </c>
-      <c r="H116" t="s">
-        <v>12</v>
-      </c>
-      <c r="I116" t="s">
-        <v>320</v>
-      </c>
-      <c r="J116" s="5" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>5</v>
-      </c>
-      <c r="B117" s="4">
-        <v>97</v>
-      </c>
-      <c r="C117" t="s">
-        <v>307</v>
-      </c>
-      <c r="D117" t="s">
-        <v>269</v>
-      </c>
-      <c r="E117" t="s">
-        <v>21</v>
-      </c>
-      <c r="F117" t="s">
-        <v>7</v>
-      </c>
-      <c r="G117" t="s">
-        <v>393</v>
-      </c>
-      <c r="H117" t="s">
-        <v>51</v>
-      </c>
-      <c r="I117" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B116" s="11">
+        <v>91</v>
+      </c>
+      <c r="C116" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="D116" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="E116" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F116" s="11">
+        <v>3</v>
+      </c>
+      <c r="G116" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="H116" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="I116" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="J116" s="12" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B117" s="11">
         <v>322</v>
       </c>
-      <c r="J117" s="5" t="s">
-        <v>323</v>
+      <c r="C117" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="D117" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="E117" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F117" s="11">
+        <v>2</v>
+      </c>
+      <c r="G117" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="H117" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="I117" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="J117" s="12" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
@@ -5251,45 +5116,60 @@
         <v>5</v>
       </c>
       <c r="B118" s="4">
-        <v>329</v>
+        <v>152</v>
       </c>
       <c r="C118" t="s">
-        <v>308</v>
+        <v>268</v>
       </c>
       <c r="D118" t="s">
+        <v>250</v>
+      </c>
+      <c r="E118" t="s">
+        <v>19</v>
+      </c>
+      <c r="G118" t="s">
+        <v>7</v>
+      </c>
+      <c r="H118" t="s">
+        <v>369</v>
+      </c>
+      <c r="I118" t="s">
         <v>269</v>
       </c>
-      <c r="E118" t="s">
-        <v>53</v>
-      </c>
-      <c r="F118" t="s">
-        <v>7</v>
-      </c>
-      <c r="H118" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>5</v>
-      </c>
-      <c r="B119" s="4">
-        <v>115</v>
-      </c>
-      <c r="C119" t="s">
-        <v>309</v>
-      </c>
-      <c r="D119" t="s">
-        <v>269</v>
-      </c>
-      <c r="E119" t="s">
-        <v>53</v>
-      </c>
-      <c r="F119" t="s">
-        <v>7</v>
-      </c>
-      <c r="H119" t="s">
-        <v>106</v>
+      <c r="J118" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B119" s="11">
+        <v>139</v>
+      </c>
+      <c r="C119" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="D119" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="E119" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F119" s="11">
+        <v>3</v>
+      </c>
+      <c r="G119" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="H119" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="I119" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="J119" s="12" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
@@ -5297,22 +5177,28 @@
         <v>5</v>
       </c>
       <c r="B120" s="4">
-        <v>72</v>
+        <v>300</v>
       </c>
       <c r="C120" t="s">
-        <v>310</v>
+        <v>272</v>
       </c>
       <c r="D120" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="E120" t="s">
-        <v>53</v>
-      </c>
-      <c r="F120" t="s">
-        <v>7</v>
+        <v>19</v>
+      </c>
+      <c r="G120" t="s">
+        <v>373</v>
       </c>
       <c r="H120" t="s">
-        <v>106</v>
+        <v>372</v>
+      </c>
+      <c r="I120" t="s">
+        <v>421</v>
+      </c>
+      <c r="J120" s="5" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
@@ -5320,22 +5206,25 @@
         <v>5</v>
       </c>
       <c r="B121" s="4">
-        <v>312</v>
+        <v>416</v>
       </c>
       <c r="C121" t="s">
-        <v>311</v>
+        <v>273</v>
       </c>
       <c r="D121" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="E121" t="s">
-        <v>53</v>
-      </c>
-      <c r="F121" t="s">
+        <v>19</v>
+      </c>
+      <c r="G121" t="s">
         <v>7</v>
       </c>
       <c r="H121" t="s">
-        <v>106</v>
+        <v>369</v>
+      </c>
+      <c r="I121" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
@@ -5343,22 +5232,25 @@
         <v>5</v>
       </c>
       <c r="B122" s="4">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="C122" t="s">
-        <v>312</v>
+        <v>274</v>
       </c>
       <c r="D122" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="E122" t="s">
-        <v>53</v>
-      </c>
-      <c r="F122" t="s">
+        <v>19</v>
+      </c>
+      <c r="G122" t="s">
         <v>7</v>
       </c>
       <c r="H122" t="s">
-        <v>106</v>
+        <v>369</v>
+      </c>
+      <c r="I122" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
@@ -5366,28 +5258,25 @@
         <v>5</v>
       </c>
       <c r="B123" s="4">
-        <v>53</v>
+        <v>1143</v>
       </c>
       <c r="C123" t="s">
-        <v>314</v>
+        <v>275</v>
       </c>
       <c r="D123" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="E123" t="s">
-        <v>21</v>
-      </c>
-      <c r="F123" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G123" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H123" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I123" t="s">
-        <v>351</v>
+        <v>280</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
@@ -5395,28 +5284,28 @@
         <v>5</v>
       </c>
       <c r="B124" s="4">
-        <v>55</v>
+        <v>309</v>
       </c>
       <c r="C124" t="s">
-        <v>315</v>
+        <v>276</v>
       </c>
       <c r="D124" t="s">
-        <v>316</v>
+        <v>250</v>
       </c>
       <c r="E124" t="s">
-        <v>21</v>
-      </c>
-      <c r="F124" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G124" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H124" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I124" t="s">
-        <v>324</v>
+        <v>294</v>
+      </c>
+      <c r="J124" s="5" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
@@ -5424,31 +5313,28 @@
         <v>5</v>
       </c>
       <c r="B125" s="4">
-        <v>45</v>
+        <v>518</v>
       </c>
       <c r="C125" t="s">
-        <v>325</v>
+        <v>281</v>
       </c>
       <c r="D125" t="s">
-        <v>316</v>
+        <v>250</v>
       </c>
       <c r="E125" t="s">
-        <v>21</v>
-      </c>
-      <c r="F125" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G125" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H125" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I125" t="s">
-        <v>326</v>
+        <v>293</v>
       </c>
       <c r="J125" s="5" t="s">
-        <v>327</v>
+        <v>295</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
@@ -5456,89 +5342,87 @@
         <v>5</v>
       </c>
       <c r="B126" s="4">
-        <v>134</v>
+        <v>494</v>
       </c>
       <c r="C126" t="s">
-        <v>328</v>
+        <v>282</v>
       </c>
       <c r="D126" t="s">
-        <v>316</v>
+        <v>250</v>
       </c>
       <c r="E126" t="s">
-        <v>21</v>
-      </c>
-      <c r="F126" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G126" t="s">
+        <v>7</v>
+      </c>
+      <c r="H126" t="s">
+        <v>369</v>
+      </c>
+      <c r="I126" t="s">
+        <v>296</v>
+      </c>
+      <c r="J126" s="5" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B127" s="11">
+        <v>221</v>
+      </c>
+      <c r="C127" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="D127" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="E127" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F127" s="11">
+        <v>2</v>
+      </c>
+      <c r="G127" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="H126" t="s">
-        <v>12</v>
-      </c>
-      <c r="I126" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>5</v>
-      </c>
-      <c r="B127" s="4">
-        <v>846</v>
-      </c>
-      <c r="C127" t="s">
-        <v>330</v>
-      </c>
-      <c r="D127" t="s">
-        <v>316</v>
-      </c>
-      <c r="E127" t="s">
-        <v>21</v>
-      </c>
-      <c r="F127" t="s">
-        <v>7</v>
-      </c>
-      <c r="G127" t="s">
-        <v>393</v>
-      </c>
-      <c r="H127" t="s">
-        <v>12</v>
-      </c>
-      <c r="I127" t="s">
-        <v>333</v>
-      </c>
-      <c r="J127" s="5" t="s">
-        <v>334</v>
-      </c>
+      <c r="H127" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="I127" s="10" t="s">
+        <v>420</v>
+      </c>
+      <c r="J127" s="12"/>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>5</v>
       </c>
       <c r="B128" s="4">
-        <v>1899</v>
+        <v>97</v>
       </c>
       <c r="C128" t="s">
-        <v>331</v>
+        <v>283</v>
       </c>
       <c r="D128" t="s">
-        <v>316</v>
+        <v>250</v>
       </c>
       <c r="E128" t="s">
-        <v>21</v>
-      </c>
-      <c r="F128" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G128" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H128" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I128" t="s">
-        <v>333</v>
+        <v>298</v>
+      </c>
+      <c r="J128" s="5" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
@@ -5546,28 +5430,19 @@
         <v>5</v>
       </c>
       <c r="B129" s="4">
-        <v>763</v>
+        <v>329</v>
       </c>
       <c r="C129" t="s">
-        <v>332</v>
+        <v>284</v>
       </c>
       <c r="D129" t="s">
-        <v>316</v>
+        <v>250</v>
       </c>
       <c r="E129" t="s">
-        <v>21</v>
-      </c>
-      <c r="F129" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="G129" t="s">
-        <v>393</v>
-      </c>
-      <c r="H129" t="s">
-        <v>12</v>
-      </c>
-      <c r="I129" t="s">
-        <v>335</v>
+        <v>7</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
@@ -5575,31 +5450,19 @@
         <v>5</v>
       </c>
       <c r="B130" s="4">
-        <v>678</v>
+        <v>115</v>
       </c>
       <c r="C130" t="s">
-        <v>336</v>
+        <v>285</v>
       </c>
       <c r="D130" t="s">
-        <v>316</v>
+        <v>250</v>
       </c>
       <c r="E130" t="s">
-        <v>21</v>
-      </c>
-      <c r="F130" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="G130" t="s">
-        <v>393</v>
-      </c>
-      <c r="H130" t="s">
-        <v>12</v>
-      </c>
-      <c r="I130" t="s">
-        <v>337</v>
-      </c>
-      <c r="J130" s="5" t="s">
-        <v>338</v>
+        <v>7</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
@@ -5607,28 +5470,19 @@
         <v>5</v>
       </c>
       <c r="B131" s="4">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="C131" t="s">
-        <v>340</v>
+        <v>286</v>
       </c>
       <c r="D131" t="s">
-        <v>339</v>
+        <v>250</v>
       </c>
       <c r="E131" t="s">
-        <v>21</v>
-      </c>
-      <c r="F131" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G131" t="s">
-        <v>393</v>
-      </c>
-      <c r="H131" t="s">
-        <v>12</v>
-      </c>
-      <c r="I131" t="s">
-        <v>346</v>
+        <v>7</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
@@ -5636,28 +5490,19 @@
         <v>5</v>
       </c>
       <c r="B132" s="4">
-        <v>56</v>
+        <v>312</v>
       </c>
       <c r="C132" t="s">
-        <v>341</v>
+        <v>287</v>
       </c>
       <c r="D132" t="s">
-        <v>339</v>
+        <v>250</v>
       </c>
       <c r="E132" t="s">
-        <v>21</v>
-      </c>
-      <c r="F132" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="G132" t="s">
-        <v>393</v>
-      </c>
-      <c r="H132" t="s">
-        <v>12</v>
-      </c>
-      <c r="I132" t="s">
-        <v>346</v>
+        <v>7</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
@@ -5665,92 +5510,71 @@
         <v>5</v>
       </c>
       <c r="B133" s="4">
-        <v>435</v>
+        <v>10</v>
       </c>
       <c r="C133" t="s">
-        <v>342</v>
+        <v>288</v>
       </c>
       <c r="D133" t="s">
-        <v>339</v>
+        <v>250</v>
       </c>
       <c r="E133" t="s">
-        <v>21</v>
-      </c>
-      <c r="F133" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G133" t="s">
-        <v>393</v>
-      </c>
-      <c r="H133" t="s">
-        <v>12</v>
-      </c>
-      <c r="I133" t="s">
-        <v>347</v>
+        <v>7</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>348</v>
-      </c>
-      <c r="B134" s="4" t="s">
-        <v>349</v>
+        <v>5</v>
+      </c>
+      <c r="B134" s="4">
+        <v>53</v>
       </c>
       <c r="C134" t="s">
-        <v>343</v>
+        <v>290</v>
       </c>
       <c r="D134" t="s">
-        <v>339</v>
+        <v>250</v>
       </c>
       <c r="E134" t="s">
-        <v>21</v>
-      </c>
-      <c r="F134" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G134" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H134" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I134" t="s">
-        <v>347</v>
-      </c>
-      <c r="J134" s="9" t="s">
-        <v>350</v>
+        <v>327</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>348</v>
-      </c>
-      <c r="B135" s="4" t="s">
-        <v>352</v>
+        <v>5</v>
+      </c>
+      <c r="B135" s="4">
+        <v>55</v>
       </c>
       <c r="C135" t="s">
-        <v>344</v>
+        <v>291</v>
       </c>
       <c r="D135" t="s">
-        <v>339</v>
+        <v>292</v>
       </c>
       <c r="E135" t="s">
-        <v>21</v>
-      </c>
-      <c r="F135" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G135" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H135" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I135" t="s">
-        <v>351</v>
-      </c>
-      <c r="J135" s="9" t="s">
-        <v>353</v>
+        <v>300</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
@@ -5758,22 +5582,28 @@
         <v>5</v>
       </c>
       <c r="B136" s="4">
-        <v>1851</v>
+        <v>45</v>
       </c>
       <c r="C136" t="s">
-        <v>345</v>
+        <v>301</v>
       </c>
       <c r="D136" t="s">
-        <v>339</v>
+        <v>292</v>
       </c>
       <c r="E136" t="s">
-        <v>53</v>
-      </c>
-      <c r="F136" t="s">
+        <v>19</v>
+      </c>
+      <c r="G136" t="s">
         <v>7</v>
       </c>
       <c r="H136" t="s">
-        <v>106</v>
+        <v>369</v>
+      </c>
+      <c r="I136" t="s">
+        <v>302</v>
+      </c>
+      <c r="J136" s="5" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
@@ -5781,31 +5611,25 @@
         <v>5</v>
       </c>
       <c r="B137" s="4">
-        <v>48</v>
+        <v>134</v>
       </c>
       <c r="C137" t="s">
-        <v>356</v>
+        <v>304</v>
       </c>
       <c r="D137" t="s">
-        <v>354</v>
+        <v>292</v>
       </c>
       <c r="E137" t="s">
-        <v>21</v>
-      </c>
-      <c r="F137" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G137" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H137" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I137" t="s">
-        <v>355</v>
-      </c>
-      <c r="J137" s="5" t="s">
-        <v>373</v>
+        <v>305</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
@@ -5813,31 +5637,28 @@
         <v>5</v>
       </c>
       <c r="B138" s="4">
-        <v>54</v>
+        <v>846</v>
       </c>
       <c r="C138" t="s">
-        <v>357</v>
+        <v>306</v>
       </c>
       <c r="D138" t="s">
-        <v>354</v>
+        <v>292</v>
       </c>
       <c r="E138" t="s">
-        <v>21</v>
-      </c>
-      <c r="F138" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G138" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H138" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I138" t="s">
-        <v>375</v>
+        <v>309</v>
       </c>
       <c r="J138" s="5" t="s">
-        <v>376</v>
+        <v>310</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
@@ -5845,31 +5666,25 @@
         <v>5</v>
       </c>
       <c r="B139" s="4">
-        <v>73</v>
+        <v>1899</v>
       </c>
       <c r="C139" t="s">
-        <v>358</v>
+        <v>307</v>
       </c>
       <c r="D139" t="s">
-        <v>354</v>
+        <v>292</v>
       </c>
       <c r="E139" t="s">
-        <v>21</v>
-      </c>
-      <c r="F139" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G139" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H139" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I139" t="s">
-        <v>377</v>
-      </c>
-      <c r="J139" s="5" t="s">
-        <v>378</v>
+        <v>309</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
@@ -5877,28 +5692,25 @@
         <v>5</v>
       </c>
       <c r="B140" s="4">
-        <v>202</v>
+        <v>763</v>
       </c>
       <c r="C140" t="s">
-        <v>359</v>
+        <v>308</v>
       </c>
       <c r="D140" t="s">
-        <v>360</v>
+        <v>292</v>
       </c>
       <c r="E140" t="s">
-        <v>6</v>
-      </c>
-      <c r="F140" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G140" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H140" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I140" t="s">
-        <v>377</v>
+        <v>311</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
@@ -5906,28 +5718,28 @@
         <v>5</v>
       </c>
       <c r="B141" s="4">
-        <v>66</v>
+        <v>678</v>
       </c>
       <c r="C141" t="s">
-        <v>361</v>
+        <v>312</v>
       </c>
       <c r="D141" t="s">
-        <v>360</v>
+        <v>292</v>
       </c>
       <c r="E141" t="s">
-        <v>6</v>
-      </c>
-      <c r="F141" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G141" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H141" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I141" t="s">
-        <v>379</v>
+        <v>313</v>
+      </c>
+      <c r="J141" s="5" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
@@ -5935,31 +5747,25 @@
         <v>5</v>
       </c>
       <c r="B142" s="4">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C142" t="s">
-        <v>362</v>
+        <v>316</v>
       </c>
       <c r="D142" t="s">
-        <v>360</v>
+        <v>315</v>
       </c>
       <c r="E142" t="s">
-        <v>21</v>
-      </c>
-      <c r="F142" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G142" t="s">
-        <v>393</v>
+        <v>38</v>
       </c>
       <c r="H142" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I142" t="s">
-        <v>380</v>
-      </c>
-      <c r="J142" s="5" t="s">
-        <v>381</v>
+        <v>322</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
@@ -5967,31 +5773,25 @@
         <v>5</v>
       </c>
       <c r="B143" s="4">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="C143" t="s">
-        <v>363</v>
+        <v>317</v>
       </c>
       <c r="D143" t="s">
-        <v>360</v>
+        <v>315</v>
       </c>
       <c r="E143" t="s">
-        <v>21</v>
-      </c>
-      <c r="F143" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G143" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H143" t="s">
-        <v>51</v>
+        <v>369</v>
       </c>
       <c r="I143" t="s">
-        <v>382</v>
-      </c>
-      <c r="J143" s="5" t="s">
-        <v>383</v>
+        <v>322</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
@@ -5999,95 +5799,83 @@
         <v>5</v>
       </c>
       <c r="B144" s="4">
-        <v>2013</v>
+        <v>435</v>
       </c>
       <c r="C144" t="s">
-        <v>364</v>
+        <v>318</v>
       </c>
       <c r="D144" t="s">
-        <v>360</v>
+        <v>315</v>
       </c>
       <c r="E144" t="s">
-        <v>21</v>
-      </c>
-      <c r="F144" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G144" t="s">
-        <v>393</v>
+        <v>38</v>
       </c>
       <c r="H144" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I144" t="s">
-        <v>384</v>
-      </c>
-      <c r="J144" s="5" t="s">
-        <v>385</v>
+        <v>323</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>5</v>
-      </c>
-      <c r="B145" s="4">
-        <v>136</v>
+        <v>324</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>325</v>
       </c>
       <c r="C145" t="s">
-        <v>365</v>
+        <v>319</v>
       </c>
       <c r="D145" t="s">
-        <v>366</v>
+        <v>315</v>
       </c>
       <c r="E145" t="s">
-        <v>6</v>
-      </c>
-      <c r="F145" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G145" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H145" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I145" t="s">
-        <v>384</v>
-      </c>
-      <c r="J145" s="5" t="s">
-        <v>386</v>
+        <v>323</v>
+      </c>
+      <c r="J145" s="6" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>5</v>
-      </c>
-      <c r="B146" s="4">
-        <v>191</v>
+        <v>324</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>328</v>
       </c>
       <c r="C146" t="s">
-        <v>367</v>
+        <v>320</v>
       </c>
       <c r="D146" t="s">
-        <v>366</v>
+        <v>315</v>
       </c>
       <c r="E146" t="s">
-        <v>6</v>
-      </c>
-      <c r="F146" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G146" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H146" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I146" t="s">
-        <v>384</v>
-      </c>
-      <c r="J146" s="5" t="s">
-        <v>387</v>
+        <v>327</v>
+      </c>
+      <c r="J146" s="6" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
@@ -6095,31 +5883,19 @@
         <v>5</v>
       </c>
       <c r="B147" s="4">
-        <v>338</v>
+        <v>1851</v>
       </c>
       <c r="C147" t="s">
-        <v>368</v>
+        <v>321</v>
       </c>
       <c r="D147" t="s">
-        <v>366</v>
+        <v>315</v>
       </c>
       <c r="E147" t="s">
-        <v>6</v>
-      </c>
-      <c r="F147" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G147" t="s">
-        <v>393</v>
-      </c>
-      <c r="H147" t="s">
-        <v>12</v>
-      </c>
-      <c r="I147" t="s">
-        <v>388</v>
-      </c>
-      <c r="J147" s="5" t="s">
-        <v>389</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
@@ -6127,31 +5903,28 @@
         <v>5</v>
       </c>
       <c r="B148" s="4">
-        <v>190</v>
+        <v>48</v>
       </c>
       <c r="C148" t="s">
-        <v>369</v>
+        <v>332</v>
       </c>
       <c r="D148" t="s">
-        <v>366</v>
+        <v>330</v>
       </c>
       <c r="E148" t="s">
-        <v>6</v>
-      </c>
-      <c r="F148" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="G148" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H148" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I148" t="s">
-        <v>388</v>
+        <v>331</v>
       </c>
       <c r="J148" s="5" t="s">
-        <v>390</v>
+        <v>349</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
@@ -6159,31 +5932,28 @@
         <v>5</v>
       </c>
       <c r="B149" s="4">
-        <v>268</v>
+        <v>54</v>
       </c>
       <c r="C149" t="s">
-        <v>370</v>
+        <v>333</v>
       </c>
       <c r="D149" t="s">
-        <v>366</v>
+        <v>330</v>
       </c>
       <c r="E149" t="s">
-        <v>6</v>
-      </c>
-      <c r="F149" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="G149" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H149" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I149" t="s">
-        <v>391</v>
+        <v>351</v>
       </c>
       <c r="J149" s="5" t="s">
-        <v>386</v>
+        <v>352</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
@@ -6191,28 +5961,28 @@
         <v>5</v>
       </c>
       <c r="B150" s="4">
-        <v>371</v>
+        <v>73</v>
       </c>
       <c r="C150" t="s">
-        <v>371</v>
+        <v>334</v>
       </c>
       <c r="D150" t="s">
-        <v>366</v>
+        <v>330</v>
       </c>
       <c r="E150" t="s">
-        <v>21</v>
-      </c>
-      <c r="F150" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="G150" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H150" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I150" t="s">
-        <v>391</v>
+        <v>353</v>
+      </c>
+      <c r="J150" s="5" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
@@ -6220,57 +5990,397 @@
         <v>5</v>
       </c>
       <c r="B151" s="4">
-        <v>7</v>
+        <v>202</v>
       </c>
       <c r="C151" t="s">
-        <v>372</v>
+        <v>335</v>
       </c>
       <c r="D151" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
       <c r="E151" t="s">
-        <v>21</v>
-      </c>
-      <c r="F151" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G151" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="H151" t="s">
-        <v>12</v>
+        <v>369</v>
       </c>
       <c r="I151" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="152" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B152" s="7"/>
-      <c r="J152" s="8"/>
+        <v>353</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>5</v>
+      </c>
+      <c r="B152" s="4">
+        <v>66</v>
+      </c>
+      <c r="C152" t="s">
+        <v>337</v>
+      </c>
+      <c r="D152" t="s">
+        <v>336</v>
+      </c>
+      <c r="E152" t="s">
+        <v>6</v>
+      </c>
+      <c r="G152" t="s">
+        <v>7</v>
+      </c>
+      <c r="H152" t="s">
+        <v>369</v>
+      </c>
+      <c r="I152" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>5</v>
+      </c>
+      <c r="B153" s="4">
+        <v>50</v>
+      </c>
+      <c r="C153" t="s">
+        <v>338</v>
+      </c>
+      <c r="D153" t="s">
+        <v>336</v>
+      </c>
+      <c r="E153" t="s">
+        <v>19</v>
+      </c>
+      <c r="G153" t="s">
+        <v>7</v>
+      </c>
+      <c r="H153" t="s">
+        <v>369</v>
+      </c>
+      <c r="I153" t="s">
+        <v>356</v>
+      </c>
+      <c r="J153" s="5" t="s">
+        <v>357</v>
+      </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>5</v>
       </c>
       <c r="B154" s="4">
-        <v>547</v>
+        <v>43</v>
       </c>
       <c r="C154" t="s">
-        <v>246</v>
+        <v>339</v>
       </c>
       <c r="D154" t="s">
-        <v>247</v>
+        <v>336</v>
       </c>
       <c r="E154" t="s">
-        <v>21</v>
+        <v>19</v>
+      </c>
+      <c r="G154" t="s">
+        <v>7</v>
+      </c>
+      <c r="H154" t="s">
+        <v>369</v>
+      </c>
+      <c r="I154" t="s">
+        <v>358</v>
+      </c>
+      <c r="J154" s="5" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>5</v>
+      </c>
+      <c r="B155" s="4">
+        <v>2013</v>
+      </c>
+      <c r="C155" t="s">
+        <v>340</v>
+      </c>
+      <c r="D155" t="s">
+        <v>336</v>
+      </c>
+      <c r="E155" t="s">
+        <v>19</v>
+      </c>
+      <c r="G155" t="s">
+        <v>7</v>
+      </c>
+      <c r="H155" t="s">
+        <v>369</v>
+      </c>
+      <c r="I155" t="s">
+        <v>360</v>
+      </c>
+      <c r="J155" s="5" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>5</v>
+      </c>
+      <c r="B156" s="4">
+        <v>136</v>
+      </c>
+      <c r="C156" t="s">
+        <v>341</v>
+      </c>
+      <c r="D156" t="s">
+        <v>342</v>
+      </c>
+      <c r="E156" t="s">
+        <v>6</v>
+      </c>
+      <c r="G156" t="s">
+        <v>7</v>
+      </c>
+      <c r="H156" t="s">
+        <v>369</v>
+      </c>
+      <c r="I156" t="s">
+        <v>360</v>
+      </c>
+      <c r="J156" s="5" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>5</v>
+      </c>
+      <c r="B157" s="4">
+        <v>191</v>
+      </c>
+      <c r="C157" t="s">
+        <v>343</v>
+      </c>
+      <c r="D157" t="s">
+        <v>342</v>
+      </c>
+      <c r="E157" t="s">
+        <v>6</v>
+      </c>
+      <c r="G157" t="s">
+        <v>7</v>
+      </c>
+      <c r="H157" t="s">
+        <v>369</v>
+      </c>
+      <c r="I157" t="s">
+        <v>360</v>
+      </c>
+      <c r="J157" s="5" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>5</v>
+      </c>
+      <c r="B158" s="4">
+        <v>338</v>
+      </c>
+      <c r="C158" t="s">
+        <v>344</v>
+      </c>
+      <c r="D158" t="s">
+        <v>342</v>
+      </c>
+      <c r="E158" t="s">
+        <v>6</v>
+      </c>
+      <c r="G158" t="s">
+        <v>38</v>
+      </c>
+      <c r="H158" t="s">
+        <v>369</v>
+      </c>
+      <c r="I158" t="s">
+        <v>364</v>
+      </c>
+      <c r="J158" s="5" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>5</v>
+      </c>
+      <c r="B159" s="4">
+        <v>190</v>
+      </c>
+      <c r="C159" t="s">
+        <v>345</v>
+      </c>
+      <c r="D159" t="s">
+        <v>342</v>
+      </c>
+      <c r="E159" t="s">
+        <v>6</v>
+      </c>
+      <c r="G159" t="s">
+        <v>38</v>
+      </c>
+      <c r="H159" t="s">
+        <v>369</v>
+      </c>
+      <c r="I159" t="s">
+        <v>364</v>
+      </c>
+      <c r="J159" s="5" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>5</v>
+      </c>
+      <c r="B160" s="4">
+        <v>268</v>
+      </c>
+      <c r="C160" t="s">
+        <v>346</v>
+      </c>
+      <c r="D160" t="s">
+        <v>342</v>
+      </c>
+      <c r="E160" t="s">
+        <v>6</v>
+      </c>
+      <c r="G160" t="s">
+        <v>38</v>
+      </c>
+      <c r="H160" t="s">
+        <v>369</v>
+      </c>
+      <c r="I160" t="s">
+        <v>367</v>
+      </c>
+      <c r="J160" s="5" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>5</v>
+      </c>
+      <c r="B161" s="4">
+        <v>371</v>
+      </c>
+      <c r="C161" t="s">
+        <v>347</v>
+      </c>
+      <c r="D161" t="s">
+        <v>342</v>
+      </c>
+      <c r="E161" t="s">
+        <v>19</v>
+      </c>
+      <c r="G161" t="s">
+        <v>38</v>
+      </c>
+      <c r="H161" t="s">
+        <v>369</v>
+      </c>
+      <c r="I161" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>5</v>
+      </c>
+      <c r="B162" s="4">
+        <v>7</v>
+      </c>
+      <c r="C162" t="s">
+        <v>348</v>
+      </c>
+      <c r="D162" t="s">
+        <v>342</v>
+      </c>
+      <c r="E162" t="s">
+        <v>19</v>
+      </c>
+      <c r="G162" t="s">
+        <v>7</v>
+      </c>
+      <c r="H162" t="s">
+        <v>369</v>
+      </c>
+      <c r="I162" t="s">
+        <v>367</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="J134" r:id="rId1" xr:uid="{4213E806-E604-4AE2-8406-2DB17397E06E}"/>
-    <hyperlink ref="J135" r:id="rId2" xr:uid="{A42CB0AD-40C9-4576-B622-DF300ED56D10}"/>
+    <hyperlink ref="J145" r:id="rId1" xr:uid="{4213E806-E604-4AE2-8406-2DB17397E06E}"/>
+    <hyperlink ref="J146" r:id="rId2" xr:uid="{A42CB0AD-40C9-4576-B622-DF300ED56D10}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63392036-0DF4-41BC-932A-0EBA4F02E5CB}">
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/docs/Programming Puzzles.xlsx
+++ b/docs/Programming Puzzles.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\Projects\ProjectDSA\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17C6764F-4D3D-4883-9E4D-0B76B36AC494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E64630B-89AE-4A68-8F76-2CD6965B9144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{B7950DC0-5F1E-48EF-9340-8CAB6CE423A3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{B7950DC0-5F1E-48EF-9340-8CAB6CE423A3}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="421">
   <si>
     <t>PLATFORM</t>
   </si>
@@ -92,12 +92,6 @@
     <t>Group Anagrams</t>
   </si>
   <si>
-    <t>Arrays, Hashmaps</t>
-  </si>
-  <si>
-    <t>Strings, Hashmaps</t>
-  </si>
-  <si>
     <t>Medium</t>
   </si>
   <si>
@@ -986,9 +980,6 @@
     <t>Alternate solution to using a stack.</t>
   </si>
   <si>
-    <t>Arrays, Intervals</t>
-  </si>
-  <si>
     <t>Insert Interval</t>
   </si>
   <si>
@@ -1305,6 +1296,12 @@
   </si>
   <si>
     <t>02/02/2026</t>
+  </si>
+  <si>
+    <t>Intervals</t>
+  </si>
+  <si>
+    <t>Hashmaps</t>
   </si>
 </sst>
 </file>
@@ -1759,14 +1756,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E29EE35E-42CE-4BB8-BA9B-83E0DF36D658}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="65.140625" customWidth="1"/>
+    <col min="1" max="1" width="65.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -1777,7 +1774,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{673553DD-7322-43E4-B8E6-8596552AA633}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1786,21 +1783,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{758F6333-ADD2-4F62-82FC-3789A0207F8D}">
   <dimension ref="A1:J162"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="52.28515625" customWidth="1"/>
-    <col min="4" max="4" width="36.42578125" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="34.5703125" customWidth="1"/>
+    <col min="1" max="1" width="18.453125" customWidth="1"/>
+    <col min="2" max="2" width="11.81640625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="52.26953125" customWidth="1"/>
+    <col min="4" max="4" width="36.453125" customWidth="1"/>
+    <col min="5" max="5" width="13.54296875" customWidth="1"/>
+    <col min="6" max="6" width="13.54296875" style="4" customWidth="1"/>
+    <col min="7" max="7" width="34.54296875" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="15.28515625" customWidth="1"/>
-    <col min="10" max="10" width="92.7109375" style="5" customWidth="1"/>
+    <col min="9" max="9" width="15.26953125" customWidth="1"/>
+    <col min="10" max="10" width="92.7265625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1817,22 +1814,22 @@
         <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1843,22 +1840,22 @@
         <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="G2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H2" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1869,7 +1866,7 @@
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>420</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -1878,13 +1875,13 @@
         <v>7</v>
       </c>
       <c r="H3" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>5</v>
       </c>
@@ -1895,7 +1892,7 @@
         <v>14</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>17</v>
+        <v>420</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>6</v>
@@ -1907,14 +1904,14 @@
         <v>7</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="J4" s="9"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1925,22 +1922,22 @@
         <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>420</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G5" t="s">
         <v>7</v>
       </c>
       <c r="H5" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1948,28 +1945,28 @@
         <v>347</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" t="s">
+        <v>366</v>
+      </c>
+      <c r="I6" t="s">
         <v>19</v>
       </c>
-      <c r="G6" t="s">
-        <v>7</v>
-      </c>
-      <c r="H6" t="s">
-        <v>369</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="J6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="J6" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1977,25 +1974,25 @@
         <v>238</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H7" t="s">
+        <v>366</v>
+      </c>
+      <c r="I7" t="s">
         <v>19</v>
       </c>
-      <c r="G7" t="s">
-        <v>7</v>
-      </c>
-      <c r="H7" t="s">
-        <v>369</v>
-      </c>
-      <c r="I7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -2003,28 +2000,28 @@
         <v>36</v>
       </c>
       <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" t="s">
         <v>26</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" t="s">
+        <v>7</v>
+      </c>
+      <c r="H8" t="s">
+        <v>366</v>
+      </c>
+      <c r="I8" t="s">
+        <v>25</v>
+      </c>
+      <c r="J8" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" t="s">
-        <v>7</v>
-      </c>
-      <c r="H8" t="s">
-        <v>369</v>
-      </c>
-      <c r="I8" t="s">
-        <v>27</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -2032,28 +2029,28 @@
         <v>271</v>
       </c>
       <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" t="s">
+        <v>184</v>
+      </c>
+      <c r="E9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H9" t="s">
+        <v>366</v>
+      </c>
+      <c r="I9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D9" t="s">
-        <v>186</v>
-      </c>
-      <c r="E9" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" t="s">
-        <v>7</v>
-      </c>
-      <c r="H9" t="s">
-        <v>369</v>
-      </c>
-      <c r="I9" t="s">
-        <v>32</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -2061,28 +2058,28 @@
         <v>128</v>
       </c>
       <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s">
+        <v>183</v>
+      </c>
+      <c r="E10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H10" t="s">
+        <v>366</v>
+      </c>
+      <c r="I10" t="s">
+        <v>33</v>
+      </c>
+      <c r="J10" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D10" t="s">
-        <v>185</v>
-      </c>
-      <c r="E10" t="s">
-        <v>19</v>
-      </c>
-      <c r="G10" t="s">
-        <v>7</v>
-      </c>
-      <c r="H10" t="s">
-        <v>369</v>
-      </c>
-      <c r="I10" t="s">
-        <v>35</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -2090,28 +2087,28 @@
         <v>125</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
       </c>
       <c r="G11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H11" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -2119,28 +2116,28 @@
         <v>167</v>
       </c>
       <c r="C12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" t="s">
+        <v>7</v>
+      </c>
+      <c r="H12" t="s">
+        <v>366</v>
+      </c>
+      <c r="I12" t="s">
         <v>40</v>
       </c>
-      <c r="D12" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" t="s">
-        <v>7</v>
-      </c>
-      <c r="H12" t="s">
-        <v>369</v>
-      </c>
-      <c r="I12" t="s">
-        <v>42</v>
-      </c>
       <c r="J12" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A13" s="10" t="s">
         <v>5</v>
       </c>
@@ -2148,13 +2145,13 @@
         <v>15</v>
       </c>
       <c r="C13" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="10" t="s">
-        <v>45</v>
-      </c>
       <c r="E13" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F13" s="11">
         <v>3</v>
@@ -2163,16 +2160,16 @@
         <v>7</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -2180,25 +2177,25 @@
         <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" t="s">
+        <v>7</v>
+      </c>
+      <c r="H14" t="s">
+        <v>366</v>
+      </c>
+      <c r="I14" t="s">
         <v>45</v>
       </c>
-      <c r="E14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G14" t="s">
-        <v>7</v>
-      </c>
-      <c r="H14" t="s">
-        <v>369</v>
-      </c>
-      <c r="I14" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -2206,28 +2203,28 @@
         <v>42</v>
       </c>
       <c r="C15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" t="s">
+        <v>47</v>
+      </c>
+      <c r="G15" t="s">
+        <v>7</v>
+      </c>
+      <c r="H15" t="s">
+        <v>366</v>
+      </c>
+      <c r="I15" t="s">
         <v>48</v>
       </c>
-      <c r="D15" t="s">
-        <v>45</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="J15" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="G15" t="s">
-        <v>7</v>
-      </c>
-      <c r="H15" t="s">
-        <v>369</v>
-      </c>
-      <c r="I15" t="s">
-        <v>50</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -2235,10 +2232,10 @@
         <v>121</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
@@ -2247,13 +2244,13 @@
         <v>7</v>
       </c>
       <c r="H16" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I16" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -2261,28 +2258,28 @@
         <v>3</v>
       </c>
       <c r="C17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" t="s">
+        <v>231</v>
+      </c>
+      <c r="E17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" t="s">
+        <v>7</v>
+      </c>
+      <c r="H17" t="s">
+        <v>366</v>
+      </c>
+      <c r="I17" t="s">
+        <v>52</v>
+      </c>
+      <c r="J17" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D17" t="s">
-        <v>233</v>
-      </c>
-      <c r="E17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G17" t="s">
-        <v>7</v>
-      </c>
-      <c r="H17" t="s">
-        <v>369</v>
-      </c>
-      <c r="I17" t="s">
-        <v>54</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -2290,28 +2287,28 @@
         <v>424</v>
       </c>
       <c r="C18" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" t="s">
+        <v>231</v>
+      </c>
+      <c r="E18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G18" t="s">
+        <v>7</v>
+      </c>
+      <c r="H18" t="s">
+        <v>366</v>
+      </c>
+      <c r="I18" t="s">
+        <v>55</v>
+      </c>
+      <c r="J18" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D18" t="s">
-        <v>233</v>
-      </c>
-      <c r="E18" t="s">
-        <v>19</v>
-      </c>
-      <c r="G18" t="s">
-        <v>7</v>
-      </c>
-      <c r="H18" t="s">
-        <v>369</v>
-      </c>
-      <c r="I18" t="s">
-        <v>57</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -2319,28 +2316,28 @@
         <v>567</v>
       </c>
       <c r="C19" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" t="s">
+        <v>231</v>
+      </c>
+      <c r="E19" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19" t="s">
+        <v>7</v>
+      </c>
+      <c r="H19" t="s">
+        <v>366</v>
+      </c>
+      <c r="I19" t="s">
+        <v>58</v>
+      </c>
+      <c r="J19" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D19" t="s">
-        <v>233</v>
-      </c>
-      <c r="E19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G19" t="s">
-        <v>7</v>
-      </c>
-      <c r="H19" t="s">
-        <v>369</v>
-      </c>
-      <c r="I19" t="s">
-        <v>60</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>5</v>
       </c>
@@ -2348,28 +2345,28 @@
         <v>76</v>
       </c>
       <c r="C20" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D20" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E20" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G20" t="s">
         <v>7</v>
       </c>
       <c r="H20" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I20" t="s">
+        <v>60</v>
+      </c>
+      <c r="J20" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="J20" s="5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -2377,28 +2374,28 @@
         <v>239</v>
       </c>
       <c r="C21" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" t="s">
+        <v>231</v>
+      </c>
+      <c r="E21" t="s">
+        <v>47</v>
+      </c>
+      <c r="G21" t="s">
+        <v>7</v>
+      </c>
+      <c r="H21" t="s">
+        <v>366</v>
+      </c>
+      <c r="I21" t="s">
+        <v>64</v>
+      </c>
+      <c r="J21" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D21" t="s">
-        <v>233</v>
-      </c>
-      <c r="E21" t="s">
-        <v>49</v>
-      </c>
-      <c r="G21" t="s">
-        <v>7</v>
-      </c>
-      <c r="H21" t="s">
-        <v>369</v>
-      </c>
-      <c r="I21" t="s">
-        <v>66</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
         <v>5</v>
       </c>
@@ -2406,10 +2403,10 @@
         <v>20</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>6</v>
@@ -2421,45 +2418,45 @@
         <v>7</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I22" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>68</v>
-      </c>
-      <c r="J22" s="9" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>70</v>
       </c>
       <c r="B23" s="4">
         <v>155</v>
       </c>
       <c r="C23" t="s">
+        <v>69</v>
+      </c>
+      <c r="D23" t="s">
+        <v>70</v>
+      </c>
+      <c r="E23" t="s">
+        <v>17</v>
+      </c>
+      <c r="G23" t="s">
+        <v>7</v>
+      </c>
+      <c r="H23" t="s">
+        <v>366</v>
+      </c>
+      <c r="I23" t="s">
+        <v>66</v>
+      </c>
+      <c r="J23" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="D23" t="s">
-        <v>72</v>
-      </c>
-      <c r="E23" t="s">
-        <v>19</v>
-      </c>
-      <c r="G23" t="s">
-        <v>7</v>
-      </c>
-      <c r="H23" t="s">
-        <v>369</v>
-      </c>
-      <c r="I23" t="s">
-        <v>68</v>
-      </c>
-      <c r="J23" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>5</v>
       </c>
@@ -2467,28 +2464,28 @@
         <v>150</v>
       </c>
       <c r="C24" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D24" t="s">
+        <v>70</v>
+      </c>
+      <c r="E24" t="s">
+        <v>17</v>
+      </c>
+      <c r="G24" t="s">
+        <v>7</v>
+      </c>
+      <c r="H24" t="s">
+        <v>366</v>
+      </c>
+      <c r="I24" t="s">
         <v>72</v>
       </c>
-      <c r="E24" t="s">
-        <v>19</v>
-      </c>
-      <c r="G24" t="s">
-        <v>7</v>
-      </c>
-      <c r="H24" t="s">
-        <v>369</v>
-      </c>
-      <c r="I24" t="s">
-        <v>74</v>
-      </c>
       <c r="J24" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -2496,28 +2493,28 @@
         <v>22</v>
       </c>
       <c r="C25" t="s">
+        <v>75</v>
+      </c>
+      <c r="D25" t="s">
+        <v>70</v>
+      </c>
+      <c r="E25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G25" t="s">
+        <v>7</v>
+      </c>
+      <c r="H25" t="s">
+        <v>366</v>
+      </c>
+      <c r="I25" t="s">
+        <v>76</v>
+      </c>
+      <c r="J25" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D25" t="s">
-        <v>72</v>
-      </c>
-      <c r="E25" t="s">
-        <v>19</v>
-      </c>
-      <c r="G25" t="s">
-        <v>7</v>
-      </c>
-      <c r="H25" t="s">
-        <v>369</v>
-      </c>
-      <c r="I25" t="s">
-        <v>78</v>
-      </c>
-      <c r="J25" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>5</v>
       </c>
@@ -2525,25 +2522,25 @@
         <v>739</v>
       </c>
       <c r="C26" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D26" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E26" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G26" t="s">
         <v>7</v>
       </c>
       <c r="H26" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I26" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -2551,28 +2548,28 @@
         <v>853</v>
       </c>
       <c r="C27" t="s">
+        <v>80</v>
+      </c>
+      <c r="D27" t="s">
+        <v>70</v>
+      </c>
+      <c r="E27" t="s">
+        <v>17</v>
+      </c>
+      <c r="G27" t="s">
+        <v>7</v>
+      </c>
+      <c r="H27" t="s">
+        <v>366</v>
+      </c>
+      <c r="I27" t="s">
+        <v>81</v>
+      </c>
+      <c r="J27" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="D27" t="s">
-        <v>72</v>
-      </c>
-      <c r="E27" t="s">
-        <v>19</v>
-      </c>
-      <c r="G27" t="s">
-        <v>7</v>
-      </c>
-      <c r="H27" t="s">
-        <v>369</v>
-      </c>
-      <c r="I27" t="s">
-        <v>83</v>
-      </c>
-      <c r="J27" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>5</v>
       </c>
@@ -2580,28 +2577,28 @@
         <v>84</v>
       </c>
       <c r="C28" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D28" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E28" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G28" t="s">
         <v>7</v>
       </c>
       <c r="H28" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I28" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -2609,10 +2606,10 @@
         <v>704</v>
       </c>
       <c r="C29" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D29" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E29" t="s">
         <v>6</v>
@@ -2621,16 +2618,16 @@
         <v>7</v>
       </c>
       <c r="H29" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I29" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>5</v>
       </c>
@@ -2638,28 +2635,28 @@
         <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D30" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E30" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G30" t="s">
         <v>7</v>
       </c>
       <c r="H30" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I30" t="s">
+        <v>86</v>
+      </c>
+      <c r="J30" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="J30" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:10" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -2667,28 +2664,28 @@
         <v>875</v>
       </c>
       <c r="C31" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D31" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E31" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G31" t="s">
         <v>7</v>
       </c>
       <c r="H31" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I31" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>5</v>
       </c>
@@ -2696,28 +2693,28 @@
         <v>33</v>
       </c>
       <c r="C32" t="s">
+        <v>91</v>
+      </c>
+      <c r="D32" t="s">
+        <v>85</v>
+      </c>
+      <c r="E32" t="s">
+        <v>17</v>
+      </c>
+      <c r="G32" t="s">
+        <v>7</v>
+      </c>
+      <c r="H32" t="s">
+        <v>366</v>
+      </c>
+      <c r="I32" t="s">
+        <v>92</v>
+      </c>
+      <c r="J32" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="D32" t="s">
-        <v>87</v>
-      </c>
-      <c r="E32" t="s">
-        <v>19</v>
-      </c>
-      <c r="G32" t="s">
-        <v>7</v>
-      </c>
-      <c r="H32" t="s">
-        <v>369</v>
-      </c>
-      <c r="I32" t="s">
-        <v>94</v>
-      </c>
-      <c r="J32" s="5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>5</v>
       </c>
@@ -2725,28 +2722,28 @@
         <v>153</v>
       </c>
       <c r="C33" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D33" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E33" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G33" t="s">
         <v>7</v>
       </c>
       <c r="H33" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I33" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>5</v>
       </c>
@@ -2754,28 +2751,28 @@
         <v>981</v>
       </c>
       <c r="C34" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D34" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E34" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G34" t="s">
         <v>7</v>
       </c>
       <c r="H34" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I34" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>5</v>
       </c>
@@ -2783,22 +2780,22 @@
         <v>4</v>
       </c>
       <c r="C35" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D35" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E35" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G35" t="s">
         <v>7</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>5</v>
       </c>
@@ -2806,22 +2803,22 @@
         <v>283</v>
       </c>
       <c r="C36" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="D36" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E36" t="s">
         <v>6</v>
       </c>
       <c r="G36" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="H36" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>5</v>
       </c>
@@ -2829,22 +2826,22 @@
         <v>876</v>
       </c>
       <c r="C37" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D37" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E37" t="s">
         <v>6</v>
       </c>
       <c r="G37" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="H37" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>5</v>
       </c>
@@ -2852,10 +2849,10 @@
         <v>206</v>
       </c>
       <c r="C38" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D38" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E38" t="s">
         <v>6</v>
@@ -2864,16 +2861,16 @@
         <v>7</v>
       </c>
       <c r="H38" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I38" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>5</v>
       </c>
@@ -2881,10 +2878,10 @@
         <v>21</v>
       </c>
       <c r="C39" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D39" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E39" t="s">
         <v>6</v>
@@ -2893,16 +2890,16 @@
         <v>7</v>
       </c>
       <c r="H39" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I39" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>5</v>
       </c>
@@ -2910,28 +2907,28 @@
         <v>143</v>
       </c>
       <c r="C40" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D40" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E40" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G40" t="s">
         <v>7</v>
       </c>
       <c r="H40" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I40" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>5</v>
       </c>
@@ -2939,28 +2936,28 @@
         <v>19</v>
       </c>
       <c r="C41" t="s">
+        <v>108</v>
+      </c>
+      <c r="D41" t="s">
+        <v>109</v>
+      </c>
+      <c r="E41" t="s">
+        <v>17</v>
+      </c>
+      <c r="G41" t="s">
+        <v>370</v>
+      </c>
+      <c r="H41" t="s">
+        <v>369</v>
+      </c>
+      <c r="I41" t="s">
+        <v>415</v>
+      </c>
+      <c r="J41" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D41" t="s">
-        <v>111</v>
-      </c>
-      <c r="E41" t="s">
-        <v>19</v>
-      </c>
-      <c r="G41" t="s">
-        <v>373</v>
-      </c>
-      <c r="H41" t="s">
-        <v>372</v>
-      </c>
-      <c r="I41" t="s">
-        <v>418</v>
-      </c>
-      <c r="J41" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>5</v>
       </c>
@@ -2968,25 +2965,25 @@
         <v>138</v>
       </c>
       <c r="C42" t="s">
+        <v>111</v>
+      </c>
+      <c r="D42" t="s">
+        <v>112</v>
+      </c>
+      <c r="E42" t="s">
+        <v>17</v>
+      </c>
+      <c r="G42" t="s">
+        <v>7</v>
+      </c>
+      <c r="H42" t="s">
+        <v>366</v>
+      </c>
+      <c r="I42" t="s">
         <v>113</v>
       </c>
-      <c r="D42" t="s">
-        <v>114</v>
-      </c>
-      <c r="E42" t="s">
-        <v>19</v>
-      </c>
-      <c r="G42" t="s">
-        <v>7</v>
-      </c>
-      <c r="H42" t="s">
-        <v>369</v>
-      </c>
-      <c r="I42" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>5</v>
       </c>
@@ -2994,28 +2991,28 @@
         <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D43" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E43" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G43" t="s">
         <v>7</v>
       </c>
       <c r="H43" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I43" t="s">
+        <v>113</v>
+      </c>
+      <c r="J43" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="J43" s="5" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>5</v>
       </c>
@@ -3023,28 +3020,28 @@
         <v>141</v>
       </c>
       <c r="C44" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D44" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E44" t="s">
         <v>6</v>
       </c>
       <c r="G44" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H44" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I44" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>5</v>
       </c>
@@ -3052,28 +3049,28 @@
         <v>287</v>
       </c>
       <c r="C45" t="s">
+        <v>118</v>
+      </c>
+      <c r="D45" t="s">
+        <v>112</v>
+      </c>
+      <c r="E45" t="s">
+        <v>17</v>
+      </c>
+      <c r="G45" t="s">
+        <v>7</v>
+      </c>
+      <c r="H45" t="s">
+        <v>366</v>
+      </c>
+      <c r="I45" t="s">
         <v>120</v>
       </c>
-      <c r="D45" t="s">
-        <v>114</v>
-      </c>
-      <c r="E45" t="s">
-        <v>19</v>
-      </c>
-      <c r="G45" t="s">
-        <v>7</v>
-      </c>
-      <c r="H45" t="s">
-        <v>369</v>
-      </c>
-      <c r="I45" t="s">
-        <v>122</v>
-      </c>
       <c r="J45" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>5</v>
       </c>
@@ -3081,25 +3078,25 @@
         <v>146</v>
       </c>
       <c r="C46" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D46" t="s">
+        <v>122</v>
+      </c>
+      <c r="E46" t="s">
+        <v>17</v>
+      </c>
+      <c r="G46" t="s">
+        <v>7</v>
+      </c>
+      <c r="H46" t="s">
+        <v>366</v>
+      </c>
+      <c r="I46" t="s">
         <v>124</v>
       </c>
-      <c r="E46" t="s">
-        <v>19</v>
-      </c>
-      <c r="G46" t="s">
-        <v>7</v>
-      </c>
-      <c r="H46" t="s">
-        <v>369</v>
-      </c>
-      <c r="I46" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>5</v>
       </c>
@@ -3107,19 +3104,19 @@
         <v>23</v>
       </c>
       <c r="C47" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D47" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E47" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G47" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>5</v>
       </c>
@@ -3127,19 +3124,19 @@
         <v>25</v>
       </c>
       <c r="C48" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="D48" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E48" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G48" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A49" s="7" t="s">
         <v>5</v>
       </c>
@@ -3147,10 +3144,10 @@
         <v>226</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E49" s="7" t="s">
         <v>6</v>
@@ -3159,17 +3156,17 @@
         <v>5</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J49" s="9"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>5</v>
       </c>
@@ -3177,28 +3174,28 @@
         <v>104</v>
       </c>
       <c r="C50" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D50" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E50" t="s">
         <v>6</v>
       </c>
       <c r="G50" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H50" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I50" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>5</v>
       </c>
@@ -3206,10 +3203,10 @@
         <v>543</v>
       </c>
       <c r="C51" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D51" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E51" t="s">
         <v>6</v>
@@ -3218,16 +3215,16 @@
         <v>7</v>
       </c>
       <c r="H51" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I51" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>5</v>
       </c>
@@ -3235,10 +3232,10 @@
         <v>110</v>
       </c>
       <c r="C52" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D52" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E52" t="s">
         <v>6</v>
@@ -3247,16 +3244,16 @@
         <v>7</v>
       </c>
       <c r="H52" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I52" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>5</v>
       </c>
@@ -3264,10 +3261,10 @@
         <v>100</v>
       </c>
       <c r="C53" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D53" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E53" t="s">
         <v>6</v>
@@ -3276,16 +3273,16 @@
         <v>7</v>
       </c>
       <c r="H53" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I53" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J53" s="5" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>5</v>
       </c>
@@ -3293,28 +3290,28 @@
         <v>572</v>
       </c>
       <c r="C54" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D54" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E54" t="s">
         <v>6</v>
       </c>
       <c r="G54" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H54" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I54" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J54" s="5" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>5</v>
       </c>
@@ -3322,28 +3319,28 @@
         <v>235</v>
       </c>
       <c r="C55" t="s">
+        <v>141</v>
+      </c>
+      <c r="D55" t="s">
+        <v>126</v>
+      </c>
+      <c r="E55" t="s">
+        <v>17</v>
+      </c>
+      <c r="G55" t="s">
+        <v>36</v>
+      </c>
+      <c r="H55" t="s">
+        <v>366</v>
+      </c>
+      <c r="I55" t="s">
+        <v>142</v>
+      </c>
+      <c r="J55" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="D55" t="s">
-        <v>128</v>
-      </c>
-      <c r="E55" t="s">
-        <v>19</v>
-      </c>
-      <c r="G55" t="s">
-        <v>38</v>
-      </c>
-      <c r="H55" t="s">
-        <v>369</v>
-      </c>
-      <c r="I55" t="s">
-        <v>144</v>
-      </c>
-      <c r="J55" s="5" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A56" s="10" t="s">
         <v>5</v>
       </c>
@@ -3351,31 +3348,31 @@
         <v>102</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F56" s="11">
         <v>3</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="H56" s="10" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="J56" s="12" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A57" s="10" t="s">
         <v>5</v>
       </c>
@@ -3383,29 +3380,29 @@
         <v>199</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F57" s="11">
         <v>3</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="J57" s="12"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>5</v>
       </c>
@@ -3413,28 +3410,28 @@
         <v>1448</v>
       </c>
       <c r="C58" t="s">
+        <v>147</v>
+      </c>
+      <c r="D58" t="s">
+        <v>126</v>
+      </c>
+      <c r="E58" t="s">
+        <v>17</v>
+      </c>
+      <c r="G58" t="s">
+        <v>7</v>
+      </c>
+      <c r="H58" t="s">
+        <v>366</v>
+      </c>
+      <c r="I58" t="s">
+        <v>148</v>
+      </c>
+      <c r="J58" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D58" t="s">
-        <v>128</v>
-      </c>
-      <c r="E58" t="s">
-        <v>19</v>
-      </c>
-      <c r="G58" t="s">
-        <v>7</v>
-      </c>
-      <c r="H58" t="s">
-        <v>369</v>
-      </c>
-      <c r="I58" t="s">
-        <v>150</v>
-      </c>
-      <c r="J58" s="5" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>5</v>
       </c>
@@ -3442,25 +3439,25 @@
         <v>98</v>
       </c>
       <c r="C59" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D59" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E59" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G59" t="s">
         <v>7</v>
       </c>
       <c r="H59" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I59" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>5</v>
       </c>
@@ -3468,28 +3465,28 @@
         <v>230</v>
       </c>
       <c r="C60" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D60" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E60" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G60" t="s">
         <v>7</v>
       </c>
       <c r="H60" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I60" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J60" s="5" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>5</v>
       </c>
@@ -3497,28 +3494,28 @@
         <v>105</v>
       </c>
       <c r="C61" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D61" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E61" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G61" t="s">
         <v>7</v>
       </c>
       <c r="H61" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I61" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J61" s="5" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>5</v>
       </c>
@@ -3526,19 +3523,19 @@
         <v>124</v>
       </c>
       <c r="C62" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D62" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E62" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G62" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>5</v>
       </c>
@@ -3546,19 +3543,19 @@
         <v>297</v>
       </c>
       <c r="C63" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D63" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E63" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G63" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>5</v>
       </c>
@@ -3566,28 +3563,28 @@
         <v>208</v>
       </c>
       <c r="C64" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D64" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E64" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G64" t="s">
         <v>7</v>
       </c>
       <c r="H64" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I64" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J64" s="5" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>5</v>
       </c>
@@ -3595,28 +3592,28 @@
         <v>211</v>
       </c>
       <c r="C65" t="s">
+        <v>163</v>
+      </c>
+      <c r="D65" t="s">
+        <v>155</v>
+      </c>
+      <c r="E65" t="s">
+        <v>17</v>
+      </c>
+      <c r="G65" t="s">
+        <v>36</v>
+      </c>
+      <c r="H65" t="s">
+        <v>366</v>
+      </c>
+      <c r="I65" t="s">
+        <v>162</v>
+      </c>
+      <c r="J65" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="D65" t="s">
-        <v>157</v>
-      </c>
-      <c r="E65" t="s">
-        <v>19</v>
-      </c>
-      <c r="G65" t="s">
-        <v>38</v>
-      </c>
-      <c r="H65" t="s">
-        <v>369</v>
-      </c>
-      <c r="I65" t="s">
-        <v>164</v>
-      </c>
-      <c r="J65" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>5</v>
       </c>
@@ -3624,16 +3621,16 @@
         <v>212</v>
       </c>
       <c r="C66" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E66" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G66" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>5</v>
       </c>
@@ -3641,10 +3638,10 @@
         <v>703</v>
       </c>
       <c r="C67" t="s">
+        <v>166</v>
+      </c>
+      <c r="D67" t="s">
         <v>168</v>
-      </c>
-      <c r="D67" t="s">
-        <v>170</v>
       </c>
       <c r="E67" t="s">
         <v>6</v>
@@ -3653,16 +3650,16 @@
         <v>7</v>
       </c>
       <c r="H67" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I67" t="s">
+        <v>167</v>
+      </c>
+      <c r="J67" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="J67" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>5</v>
       </c>
@@ -3670,10 +3667,10 @@
         <v>1046</v>
       </c>
       <c r="C68" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D68" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E68" t="s">
         <v>6</v>
@@ -3682,16 +3679,16 @@
         <v>7</v>
       </c>
       <c r="H68" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I68" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J68" s="5" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A69" s="10" t="s">
         <v>5</v>
       </c>
@@ -3699,31 +3696,31 @@
         <v>973</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F69" s="11">
         <v>3</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="I69" s="10" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="J69" s="12" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" s="7" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" s="7" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="7" t="s">
         <v>5</v>
       </c>
@@ -3731,31 +3728,31 @@
         <v>215</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F70" s="8">
         <v>5</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="H70" s="7" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="I70" s="7" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="J70" s="9" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>5</v>
       </c>
@@ -3763,27 +3760,27 @@
         <v>378</v>
       </c>
       <c r="C71" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="D71" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E71" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F71"/>
       <c r="G71" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="H71" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="I71" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="J71"/>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>5</v>
       </c>
@@ -3791,28 +3788,28 @@
         <v>621</v>
       </c>
       <c r="C72" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D72" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E72" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G72" t="s">
         <v>7</v>
       </c>
       <c r="H72" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I72" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J72" s="5" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>5</v>
       </c>
@@ -3820,28 +3817,28 @@
         <v>355</v>
       </c>
       <c r="C73" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D73" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E73" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G73" t="s">
         <v>7</v>
       </c>
       <c r="H73" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I73" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J73" s="5" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A74" s="10" t="s">
         <v>5</v>
       </c>
@@ -3849,31 +3846,31 @@
         <v>23</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F74" s="11">
         <v>2</v>
       </c>
       <c r="G74" s="10" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="H74" s="10" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="I74" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="J74" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J74" s="12" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>5</v>
       </c>
@@ -3881,22 +3878,22 @@
         <v>295</v>
       </c>
       <c r="C75" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D75" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E75" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G75" t="s">
         <v>7</v>
       </c>
       <c r="J75" s="5" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A76" s="10" t="s">
         <v>5</v>
       </c>
@@ -3904,31 +3901,31 @@
         <v>76</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F76" s="11">
         <v>3</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="H76" s="10" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="I76" s="10" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="J76" s="12" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A77" s="10" t="s">
         <v>5</v>
       </c>
@@ -3936,31 +3933,31 @@
         <v>39</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F77" s="11">
         <v>3</v>
       </c>
       <c r="G77" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="H77" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="I77" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="J77" s="12" t="s">
         <v>379</v>
       </c>
-      <c r="H77" s="10" t="s">
-        <v>372</v>
-      </c>
-      <c r="I77" s="10" t="s">
-        <v>380</v>
-      </c>
-      <c r="J77" s="12" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>5</v>
       </c>
@@ -3968,28 +3965,28 @@
         <v>46</v>
       </c>
       <c r="C78" t="s">
+        <v>189</v>
+      </c>
+      <c r="D78" t="s">
+        <v>181</v>
+      </c>
+      <c r="E78" t="s">
+        <v>17</v>
+      </c>
+      <c r="G78" t="s">
+        <v>7</v>
+      </c>
+      <c r="H78" t="s">
+        <v>366</v>
+      </c>
+      <c r="I78" t="s">
+        <v>190</v>
+      </c>
+      <c r="J78" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="D78" t="s">
-        <v>183</v>
-      </c>
-      <c r="E78" t="s">
-        <v>19</v>
-      </c>
-      <c r="G78" t="s">
-        <v>7</v>
-      </c>
-      <c r="H78" t="s">
-        <v>369</v>
-      </c>
-      <c r="I78" t="s">
-        <v>192</v>
-      </c>
-      <c r="J78" s="5" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>5</v>
       </c>
@@ -3997,28 +3994,28 @@
         <v>90</v>
       </c>
       <c r="C79" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D79" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E79" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G79" t="s">
         <v>7</v>
       </c>
       <c r="H79" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I79" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="J79" s="5" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>5</v>
       </c>
@@ -4026,28 +4023,28 @@
         <v>40</v>
       </c>
       <c r="C80" t="s">
+        <v>194</v>
+      </c>
+      <c r="D80" t="s">
+        <v>181</v>
+      </c>
+      <c r="E80" t="s">
+        <v>17</v>
+      </c>
+      <c r="G80" t="s">
+        <v>7</v>
+      </c>
+      <c r="H80" t="s">
+        <v>366</v>
+      </c>
+      <c r="I80" t="s">
+        <v>195</v>
+      </c>
+      <c r="J80" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="D80" t="s">
-        <v>183</v>
-      </c>
-      <c r="E80" t="s">
-        <v>19</v>
-      </c>
-      <c r="G80" t="s">
-        <v>7</v>
-      </c>
-      <c r="H80" t="s">
-        <v>369</v>
-      </c>
-      <c r="I80" t="s">
-        <v>197</v>
-      </c>
-      <c r="J80" s="5" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>5</v>
       </c>
@@ -4055,25 +4052,25 @@
         <v>79</v>
       </c>
       <c r="C81" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D81" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E81" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G81" t="s">
         <v>7</v>
       </c>
       <c r="H81" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I81" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A82" s="10" t="s">
         <v>5</v>
       </c>
@@ -4081,13 +4078,13 @@
         <v>131</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F82" s="11">
         <v>2</v>
@@ -4096,16 +4093,16 @@
         <v>7</v>
       </c>
       <c r="H82" s="10" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="I82" s="10" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="J82" s="12" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A83" s="10" t="s">
         <v>5</v>
       </c>
@@ -4113,29 +4110,29 @@
         <v>17</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F83" s="11">
         <v>3</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="I83" s="10" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="J83" s="12"/>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>5</v>
       </c>
@@ -4143,19 +4140,19 @@
         <v>51</v>
       </c>
       <c r="C84" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D84" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E84" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G84" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="85" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A85" s="10" t="s">
         <v>5</v>
       </c>
@@ -4163,31 +4160,31 @@
         <v>200</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F85" s="11">
         <v>3</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="I85" s="10" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="J85" s="12" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>5</v>
       </c>
@@ -4195,28 +4192,28 @@
         <v>133</v>
       </c>
       <c r="C86" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D86" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E86" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G86" t="s">
         <v>7</v>
       </c>
       <c r="H86" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I86" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J86" s="5" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>5</v>
       </c>
@@ -4224,28 +4221,28 @@
         <v>695</v>
       </c>
       <c r="C87" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D87" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E87" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G87" t="s">
         <v>7</v>
       </c>
       <c r="H87" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I87" t="s">
+        <v>212</v>
+      </c>
+      <c r="J87" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="J87" s="5" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>5</v>
       </c>
@@ -4253,28 +4250,28 @@
         <v>417</v>
       </c>
       <c r="C88" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D88" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E88" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G88" t="s">
         <v>7</v>
       </c>
       <c r="H88" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I88" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="J88" s="5" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>5</v>
       </c>
@@ -4282,28 +4279,28 @@
         <v>130</v>
       </c>
       <c r="C89" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D89" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E89" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G89" t="s">
         <v>7</v>
       </c>
       <c r="H89" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I89" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="J89" s="5" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>5</v>
       </c>
@@ -4311,25 +4308,25 @@
         <v>994</v>
       </c>
       <c r="C90" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D90" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E90" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G90" t="s">
         <v>7</v>
       </c>
       <c r="H90" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I90" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" s="10" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A91" s="10" t="s">
         <v>5</v>
       </c>
@@ -4337,31 +4334,31 @@
         <v>286</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F91" s="11">
         <v>3</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="I91" s="10" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="J91" s="12" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A92" s="10" t="s">
         <v>5</v>
       </c>
@@ -4369,31 +4366,31 @@
         <v>207</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E92" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F92" s="11">
         <v>3</v>
       </c>
       <c r="G92" s="10" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="H92" s="10" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="I92" s="10" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="J92" s="12" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>5</v>
       </c>
@@ -4401,28 +4398,28 @@
         <v>210</v>
       </c>
       <c r="C93" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D93" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E93" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G93" t="s">
         <v>7</v>
       </c>
       <c r="H93" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I93" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="J93" s="5" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>5</v>
       </c>
@@ -4430,28 +4427,28 @@
         <v>684</v>
       </c>
       <c r="C94" t="s">
+        <v>220</v>
+      </c>
+      <c r="D94" t="s">
+        <v>203</v>
+      </c>
+      <c r="E94" t="s">
+        <v>17</v>
+      </c>
+      <c r="G94" t="s">
+        <v>7</v>
+      </c>
+      <c r="H94" t="s">
+        <v>366</v>
+      </c>
+      <c r="I94" t="s">
         <v>222</v>
       </c>
-      <c r="D94" t="s">
-        <v>205</v>
-      </c>
-      <c r="E94" t="s">
-        <v>19</v>
-      </c>
-      <c r="G94" t="s">
-        <v>7</v>
-      </c>
-      <c r="H94" t="s">
-        <v>369</v>
-      </c>
-      <c r="I94" t="s">
-        <v>224</v>
-      </c>
       <c r="J94" s="5" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>5</v>
       </c>
@@ -4459,57 +4456,57 @@
         <v>323</v>
       </c>
       <c r="C95" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D95" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E95" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G95" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H95" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I95" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="J95" s="5" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B96" s="4">
         <v>261</v>
       </c>
       <c r="C96" t="s">
+        <v>228</v>
+      </c>
+      <c r="D96" t="s">
+        <v>203</v>
+      </c>
+      <c r="E96" t="s">
+        <v>17</v>
+      </c>
+      <c r="G96" t="s">
+        <v>36</v>
+      </c>
+      <c r="H96" t="s">
+        <v>366</v>
+      </c>
+      <c r="I96" t="s">
+        <v>229</v>
+      </c>
+      <c r="J96" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="D96" t="s">
-        <v>205</v>
-      </c>
-      <c r="E96" t="s">
-        <v>19</v>
-      </c>
-      <c r="G96" t="s">
-        <v>38</v>
-      </c>
-      <c r="H96" t="s">
-        <v>369</v>
-      </c>
-      <c r="I96" t="s">
-        <v>231</v>
-      </c>
-      <c r="J96" s="5" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="97" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A97" s="10" t="s">
         <v>5</v>
       </c>
@@ -4517,31 +4514,31 @@
         <v>127</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F97" s="11">
         <v>3</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="I97" s="10" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="J97" s="12" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>5</v>
       </c>
@@ -4549,19 +4546,19 @@
         <v>332</v>
       </c>
       <c r="C98" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D98" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E98" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G98" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>5</v>
       </c>
@@ -4569,28 +4566,28 @@
         <v>1584</v>
       </c>
       <c r="C99" t="s">
+        <v>235</v>
+      </c>
+      <c r="D99" t="s">
+        <v>203</v>
+      </c>
+      <c r="E99" t="s">
+        <v>17</v>
+      </c>
+      <c r="G99" t="s">
+        <v>7</v>
+      </c>
+      <c r="H99" t="s">
+        <v>366</v>
+      </c>
+      <c r="I99" t="s">
+        <v>236</v>
+      </c>
+      <c r="J99" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="D99" t="s">
-        <v>205</v>
-      </c>
-      <c r="E99" t="s">
-        <v>19</v>
-      </c>
-      <c r="G99" t="s">
-        <v>7</v>
-      </c>
-      <c r="H99" t="s">
-        <v>369</v>
-      </c>
-      <c r="I99" t="s">
-        <v>238</v>
-      </c>
-      <c r="J99" s="5" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>5</v>
       </c>
@@ -4598,28 +4595,28 @@
         <v>743</v>
       </c>
       <c r="C100" t="s">
+        <v>238</v>
+      </c>
+      <c r="D100" t="s">
+        <v>203</v>
+      </c>
+      <c r="E100" t="s">
+        <v>17</v>
+      </c>
+      <c r="G100" t="s">
+        <v>7</v>
+      </c>
+      <c r="H100" t="s">
+        <v>366</v>
+      </c>
+      <c r="I100" t="s">
         <v>240</v>
       </c>
-      <c r="D100" t="s">
-        <v>205</v>
-      </c>
-      <c r="E100" t="s">
-        <v>19</v>
-      </c>
-      <c r="G100" t="s">
-        <v>7</v>
-      </c>
-      <c r="H100" t="s">
-        <v>369</v>
-      </c>
-      <c r="I100" t="s">
-        <v>242</v>
-      </c>
       <c r="J100" s="5" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>5</v>
       </c>
@@ -4627,19 +4624,19 @@
         <v>778</v>
       </c>
       <c r="C101" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D101" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E101" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G101" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>5</v>
       </c>
@@ -4647,22 +4644,22 @@
         <v>269</v>
       </c>
       <c r="C102" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D102" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E102" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G102" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="H102" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>5</v>
       </c>
@@ -4670,28 +4667,28 @@
         <v>787</v>
       </c>
       <c r="C103" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D103" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E103" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G103" t="s">
         <v>7</v>
       </c>
       <c r="H103" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I103" t="s">
+        <v>244</v>
+      </c>
+      <c r="J103" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="J103" s="5" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="104" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A104" s="10" t="s">
         <v>5</v>
       </c>
@@ -4699,31 +4696,31 @@
         <v>725</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E104" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F104" s="11">
         <v>2</v>
       </c>
       <c r="G104" s="10" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="H104" s="10" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="I104" s="10" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="J104" s="12" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" s="10" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A105" s="10" t="s">
         <v>5</v>
       </c>
@@ -4731,31 +4728,31 @@
         <v>773</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F105" s="11">
         <v>2</v>
       </c>
       <c r="G105" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="H105" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="I105" s="10" t="s">
+        <v>392</v>
+      </c>
+      <c r="J105" s="12" t="s">
         <v>393</v>
       </c>
-      <c r="H105" s="10" t="s">
-        <v>390</v>
-      </c>
-      <c r="I105" s="10" t="s">
-        <v>395</v>
-      </c>
-      <c r="J105" s="12" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="106" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A106" s="10" t="s">
         <v>5</v>
       </c>
@@ -4763,95 +4760,95 @@
         <v>444</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E106" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F106" s="11">
         <v>2</v>
       </c>
       <c r="G106" s="10" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="H106" s="10" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="I106" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="J106" s="12" t="s">
         <v>399</v>
       </c>
-      <c r="J106" s="12" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="107" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A107" s="10" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B107" s="10" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F107" s="11">
         <v>3</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="I107" s="10" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="J107" s="12" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A108" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="B108" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="C108" s="10" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="108" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="10" t="s">
-        <v>398</v>
-      </c>
-      <c r="B108" s="10" t="s">
-        <v>398</v>
-      </c>
-      <c r="C108" s="10" t="s">
-        <v>403</v>
-      </c>
       <c r="D108" s="10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E108" s="10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F108" s="11">
         <v>2</v>
       </c>
       <c r="G108" s="10" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="H108" s="10" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="I108" s="10" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="J108" s="12" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>5</v>
       </c>
@@ -4859,18 +4856,18 @@
         <v>547</v>
       </c>
       <c r="C109" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D109" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E109" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F109"/>
       <c r="J109"/>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>5</v>
       </c>
@@ -4878,28 +4875,28 @@
         <v>70</v>
       </c>
       <c r="C110" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D110" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E110" t="s">
         <v>6</v>
       </c>
       <c r="G110" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H110" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I110" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J110" s="5" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A111" s="10" t="s">
         <v>5</v>
       </c>
@@ -4907,10 +4904,10 @@
         <v>746</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>6</v>
@@ -4919,19 +4916,19 @@
         <v>3</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="I111" s="10" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="J111" s="12" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A112" s="10" t="s">
         <v>5</v>
       </c>
@@ -4939,31 +4936,31 @@
         <v>198</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E112" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F112" s="11">
         <v>3</v>
       </c>
       <c r="G112" s="10" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="H112" s="10" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="I112" s="10" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="J112" s="12" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>5</v>
       </c>
@@ -4971,57 +4968,57 @@
         <v>213</v>
       </c>
       <c r="C113" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D113" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E113" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G113" t="s">
         <v>7</v>
       </c>
       <c r="H113" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I113" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="J113" s="5" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>5</v>
+      </c>
+      <c r="B114" s="4">
+        <v>5</v>
+      </c>
+      <c r="C114" t="s">
+        <v>258</v>
+      </c>
+      <c r="D114" t="s">
+        <v>248</v>
+      </c>
+      <c r="E114" t="s">
+        <v>17</v>
+      </c>
+      <c r="G114" t="s">
+        <v>36</v>
+      </c>
+      <c r="H114" t="s">
+        <v>366</v>
+      </c>
+      <c r="I114" t="s">
+        <v>261</v>
+      </c>
+      <c r="J114" s="5" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>5</v>
-      </c>
-      <c r="B114" s="4">
-        <v>5</v>
-      </c>
-      <c r="C114" t="s">
-        <v>260</v>
-      </c>
-      <c r="D114" t="s">
-        <v>250</v>
-      </c>
-      <c r="E114" t="s">
-        <v>19</v>
-      </c>
-      <c r="G114" t="s">
-        <v>38</v>
-      </c>
-      <c r="H114" t="s">
-        <v>369</v>
-      </c>
-      <c r="I114" t="s">
-        <v>263</v>
-      </c>
-      <c r="J114" s="5" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>5</v>
       </c>
@@ -5029,25 +5026,25 @@
         <v>647</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D115" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E115" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G115" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H115" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I115" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A116" s="10" t="s">
         <v>5</v>
       </c>
@@ -5055,31 +5052,31 @@
         <v>91</v>
       </c>
       <c r="C116" s="10" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D116" s="10" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="E116" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F116" s="11">
         <v>3</v>
       </c>
       <c r="G116" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="H116" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="I116" s="10" t="s">
         <v>373</v>
       </c>
-      <c r="H116" s="10" t="s">
-        <v>372</v>
-      </c>
-      <c r="I116" s="10" t="s">
-        <v>376</v>
-      </c>
       <c r="J116" s="12" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A117" s="10" t="s">
         <v>5</v>
       </c>
@@ -5087,31 +5084,31 @@
         <v>322</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D117" s="10" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F117" s="11">
         <v>2</v>
       </c>
       <c r="G117" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="H117" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="I117" s="10" t="s">
         <v>373</v>
       </c>
-      <c r="H117" s="10" t="s">
-        <v>372</v>
-      </c>
-      <c r="I117" s="10" t="s">
-        <v>376</v>
-      </c>
       <c r="J117" s="12" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>5</v>
       </c>
@@ -5119,28 +5116,28 @@
         <v>152</v>
       </c>
       <c r="C118" t="s">
+        <v>266</v>
+      </c>
+      <c r="D118" t="s">
+        <v>248</v>
+      </c>
+      <c r="E118" t="s">
+        <v>17</v>
+      </c>
+      <c r="G118" t="s">
+        <v>7</v>
+      </c>
+      <c r="H118" t="s">
+        <v>366</v>
+      </c>
+      <c r="I118" t="s">
+        <v>267</v>
+      </c>
+      <c r="J118" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="D118" t="s">
-        <v>250</v>
-      </c>
-      <c r="E118" t="s">
-        <v>19</v>
-      </c>
-      <c r="G118" t="s">
-        <v>7</v>
-      </c>
-      <c r="H118" t="s">
-        <v>369</v>
-      </c>
-      <c r="I118" t="s">
-        <v>269</v>
-      </c>
-      <c r="J118" s="5" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="119" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A119" s="10" t="s">
         <v>5</v>
       </c>
@@ -5148,31 +5145,31 @@
         <v>139</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D119" s="10" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F119" s="11">
         <v>3</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="I119" s="10" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="J119" s="12" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>5</v>
       </c>
@@ -5180,28 +5177,28 @@
         <v>300</v>
       </c>
       <c r="C120" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D120" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E120" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G120" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="H120" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="I120" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="J120" s="5" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>5</v>
       </c>
@@ -5209,25 +5206,25 @@
         <v>416</v>
       </c>
       <c r="C121" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D121" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E121" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G121" t="s">
         <v>7</v>
       </c>
       <c r="H121" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I121" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>5</v>
       </c>
@@ -5235,25 +5232,25 @@
         <v>62</v>
       </c>
       <c r="C122" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D122" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E122" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G122" t="s">
         <v>7</v>
       </c>
       <c r="H122" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I122" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>5</v>
       </c>
@@ -5261,25 +5258,25 @@
         <v>1143</v>
       </c>
       <c r="C123" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D123" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E123" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G123" t="s">
         <v>7</v>
       </c>
       <c r="H123" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I123" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>5</v>
       </c>
@@ -5287,28 +5284,28 @@
         <v>309</v>
       </c>
       <c r="C124" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D124" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E124" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G124" t="s">
         <v>7</v>
       </c>
       <c r="H124" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I124" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="J124" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>5</v>
       </c>
@@ -5316,28 +5313,28 @@
         <v>518</v>
       </c>
       <c r="C125" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D125" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E125" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G125" t="s">
         <v>7</v>
       </c>
       <c r="H125" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I125" t="s">
+        <v>291</v>
+      </c>
+      <c r="J125" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="J125" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>5</v>
       </c>
@@ -5345,28 +5342,28 @@
         <v>494</v>
       </c>
       <c r="C126" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D126" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E126" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G126" t="s">
         <v>7</v>
       </c>
       <c r="H126" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I126" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J126" s="5" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A127" s="10" t="s">
         <v>5</v>
       </c>
@@ -5374,29 +5371,29 @@
         <v>221</v>
       </c>
       <c r="C127" s="10" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D127" s="10" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F127" s="11">
         <v>2</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="I127" s="10" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="J127" s="12"/>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>5</v>
       </c>
@@ -5404,28 +5401,28 @@
         <v>97</v>
       </c>
       <c r="C128" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D128" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E128" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G128" t="s">
         <v>7</v>
       </c>
       <c r="H128" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I128" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J128" s="5" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>5</v>
       </c>
@@ -5433,19 +5430,19 @@
         <v>329</v>
       </c>
       <c r="C129" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D129" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E129" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G129" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>5</v>
       </c>
@@ -5453,19 +5450,19 @@
         <v>115</v>
       </c>
       <c r="C130" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D130" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E130" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G130" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>5</v>
       </c>
@@ -5473,19 +5470,19 @@
         <v>72</v>
       </c>
       <c r="C131" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D131" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E131" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G131" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>5</v>
       </c>
@@ -5493,19 +5490,19 @@
         <v>312</v>
       </c>
       <c r="C132" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D132" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E132" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G132" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>5</v>
       </c>
@@ -5513,19 +5510,19 @@
         <v>10</v>
       </c>
       <c r="C133" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D133" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E133" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G133" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>5</v>
       </c>
@@ -5533,25 +5530,25 @@
         <v>53</v>
       </c>
       <c r="C134" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D134" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E134" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G134" t="s">
         <v>7</v>
       </c>
       <c r="H134" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I134" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>5</v>
       </c>
@@ -5559,25 +5556,25 @@
         <v>55</v>
       </c>
       <c r="C135" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D135" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E135" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G135" t="s">
         <v>7</v>
       </c>
       <c r="H135" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I135" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>5</v>
       </c>
@@ -5585,28 +5582,28 @@
         <v>45</v>
       </c>
       <c r="C136" t="s">
+        <v>299</v>
+      </c>
+      <c r="D136" t="s">
+        <v>290</v>
+      </c>
+      <c r="E136" t="s">
+        <v>17</v>
+      </c>
+      <c r="G136" t="s">
+        <v>7</v>
+      </c>
+      <c r="H136" t="s">
+        <v>366</v>
+      </c>
+      <c r="I136" t="s">
+        <v>300</v>
+      </c>
+      <c r="J136" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="D136" t="s">
-        <v>292</v>
-      </c>
-      <c r="E136" t="s">
-        <v>19</v>
-      </c>
-      <c r="G136" t="s">
-        <v>7</v>
-      </c>
-      <c r="H136" t="s">
-        <v>369</v>
-      </c>
-      <c r="I136" t="s">
-        <v>302</v>
-      </c>
-      <c r="J136" s="5" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>5</v>
       </c>
@@ -5614,25 +5611,25 @@
         <v>134</v>
       </c>
       <c r="C137" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D137" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E137" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G137" t="s">
         <v>7</v>
       </c>
       <c r="H137" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I137" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>5</v>
       </c>
@@ -5640,28 +5637,28 @@
         <v>846</v>
       </c>
       <c r="C138" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D138" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E138" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G138" t="s">
         <v>7</v>
       </c>
       <c r="H138" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I138" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J138" s="5" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>5</v>
       </c>
@@ -5669,25 +5666,25 @@
         <v>1899</v>
       </c>
       <c r="C139" t="s">
+        <v>305</v>
+      </c>
+      <c r="D139" t="s">
+        <v>290</v>
+      </c>
+      <c r="E139" t="s">
+        <v>17</v>
+      </c>
+      <c r="G139" t="s">
+        <v>7</v>
+      </c>
+      <c r="H139" t="s">
+        <v>366</v>
+      </c>
+      <c r="I139" t="s">
         <v>307</v>
       </c>
-      <c r="D139" t="s">
-        <v>292</v>
-      </c>
-      <c r="E139" t="s">
-        <v>19</v>
-      </c>
-      <c r="G139" t="s">
-        <v>7</v>
-      </c>
-      <c r="H139" t="s">
-        <v>369</v>
-      </c>
-      <c r="I139" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>5</v>
       </c>
@@ -5695,25 +5692,25 @@
         <v>763</v>
       </c>
       <c r="C140" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D140" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E140" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G140" t="s">
         <v>7</v>
       </c>
       <c r="H140" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I140" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>5</v>
       </c>
@@ -5721,28 +5718,28 @@
         <v>678</v>
       </c>
       <c r="C141" t="s">
+        <v>310</v>
+      </c>
+      <c r="D141" t="s">
+        <v>290</v>
+      </c>
+      <c r="E141" t="s">
+        <v>17</v>
+      </c>
+      <c r="G141" t="s">
+        <v>7</v>
+      </c>
+      <c r="H141" t="s">
+        <v>366</v>
+      </c>
+      <c r="I141" t="s">
+        <v>311</v>
+      </c>
+      <c r="J141" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="D141" t="s">
-        <v>292</v>
-      </c>
-      <c r="E141" t="s">
-        <v>19</v>
-      </c>
-      <c r="G141" t="s">
-        <v>7</v>
-      </c>
-      <c r="H141" t="s">
-        <v>369</v>
-      </c>
-      <c r="I141" t="s">
-        <v>313</v>
-      </c>
-      <c r="J141" s="5" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>5</v>
       </c>
@@ -5750,25 +5747,25 @@
         <v>57</v>
       </c>
       <c r="C142" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D142" t="s">
-        <v>315</v>
+        <v>419</v>
       </c>
       <c r="E142" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G142" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H142" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I142" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>5</v>
       </c>
@@ -5776,25 +5773,25 @@
         <v>56</v>
       </c>
       <c r="C143" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D143" t="s">
-        <v>315</v>
+        <v>419</v>
       </c>
       <c r="E143" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G143" t="s">
         <v>7</v>
       </c>
       <c r="H143" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I143" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>5</v>
       </c>
@@ -5802,83 +5799,83 @@
         <v>435</v>
       </c>
       <c r="C144" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D144" t="s">
-        <v>315</v>
+        <v>419</v>
       </c>
       <c r="E144" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G144" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H144" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I144" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
+        <v>321</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="C145" t="s">
+        <v>316</v>
+      </c>
+      <c r="D145" t="s">
+        <v>419</v>
+      </c>
+      <c r="E145" t="s">
+        <v>17</v>
+      </c>
+      <c r="G145" t="s">
+        <v>7</v>
+      </c>
+      <c r="H145" t="s">
+        <v>366</v>
+      </c>
+      <c r="I145" t="s">
+        <v>320</v>
+      </c>
+      <c r="J145" s="6" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
+        <v>321</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="C146" t="s">
+        <v>317</v>
+      </c>
+      <c r="D146" t="s">
+        <v>419</v>
+      </c>
+      <c r="E146" t="s">
+        <v>17</v>
+      </c>
+      <c r="G146" t="s">
+        <v>7</v>
+      </c>
+      <c r="H146" t="s">
+        <v>366</v>
+      </c>
+      <c r="I146" t="s">
         <v>324</v>
       </c>
-      <c r="B145" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="C145" t="s">
-        <v>319</v>
-      </c>
-      <c r="D145" t="s">
-        <v>315</v>
-      </c>
-      <c r="E145" t="s">
-        <v>19</v>
-      </c>
-      <c r="G145" t="s">
-        <v>7</v>
-      </c>
-      <c r="H145" t="s">
-        <v>369</v>
-      </c>
-      <c r="I145" t="s">
-        <v>323</v>
-      </c>
-      <c r="J145" s="6" t="s">
+      <c r="J146" s="6" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>324</v>
-      </c>
-      <c r="B146" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="C146" t="s">
-        <v>320</v>
-      </c>
-      <c r="D146" t="s">
-        <v>315</v>
-      </c>
-      <c r="E146" t="s">
-        <v>19</v>
-      </c>
-      <c r="G146" t="s">
-        <v>7</v>
-      </c>
-      <c r="H146" t="s">
-        <v>369</v>
-      </c>
-      <c r="I146" t="s">
-        <v>327</v>
-      </c>
-      <c r="J146" s="6" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>5</v>
       </c>
@@ -5886,19 +5883,19 @@
         <v>1851</v>
       </c>
       <c r="C147" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D147" t="s">
-        <v>315</v>
+        <v>419</v>
       </c>
       <c r="E147" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G147" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>5</v>
       </c>
@@ -5906,28 +5903,28 @@
         <v>48</v>
       </c>
       <c r="C148" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D148" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="E148" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G148" t="s">
         <v>7</v>
       </c>
       <c r="H148" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I148" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="J148" s="5" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>5</v>
       </c>
@@ -5935,28 +5932,28 @@
         <v>54</v>
       </c>
       <c r="C149" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D149" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="E149" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G149" t="s">
         <v>7</v>
       </c>
       <c r="H149" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I149" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="J149" s="5" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>5</v>
       </c>
@@ -5964,28 +5961,28 @@
         <v>73</v>
       </c>
       <c r="C150" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D150" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="E150" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G150" t="s">
         <v>7</v>
       </c>
       <c r="H150" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I150" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="J150" s="5" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>5</v>
       </c>
@@ -5993,10 +5990,10 @@
         <v>202</v>
       </c>
       <c r="C151" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D151" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E151" t="s">
         <v>6</v>
@@ -6005,13 +6002,13 @@
         <v>7</v>
       </c>
       <c r="H151" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I151" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>5</v>
       </c>
@@ -6019,10 +6016,10 @@
         <v>66</v>
       </c>
       <c r="C152" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="D152" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E152" t="s">
         <v>6</v>
@@ -6031,13 +6028,13 @@
         <v>7</v>
       </c>
       <c r="H152" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I152" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>5</v>
       </c>
@@ -6045,28 +6042,28 @@
         <v>50</v>
       </c>
       <c r="C153" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D153" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E153" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G153" t="s">
         <v>7</v>
       </c>
       <c r="H153" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I153" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="J153" s="5" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>5</v>
       </c>
@@ -6074,28 +6071,28 @@
         <v>43</v>
       </c>
       <c r="C154" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="D154" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E154" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G154" t="s">
         <v>7</v>
       </c>
       <c r="H154" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I154" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="J154" s="5" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>5</v>
       </c>
@@ -6103,28 +6100,28 @@
         <v>2013</v>
       </c>
       <c r="C155" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D155" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E155" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G155" t="s">
         <v>7</v>
       </c>
       <c r="H155" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I155" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="J155" s="5" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>5</v>
       </c>
@@ -6132,10 +6129,10 @@
         <v>136</v>
       </c>
       <c r="C156" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D156" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E156" t="s">
         <v>6</v>
@@ -6144,16 +6141,16 @@
         <v>7</v>
       </c>
       <c r="H156" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I156" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="J156" s="5" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>5</v>
       </c>
@@ -6161,10 +6158,10 @@
         <v>191</v>
       </c>
       <c r="C157" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D157" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E157" t="s">
         <v>6</v>
@@ -6173,16 +6170,16 @@
         <v>7</v>
       </c>
       <c r="H157" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I157" t="s">
+        <v>357</v>
+      </c>
+      <c r="J157" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="J157" s="5" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>5</v>
       </c>
@@ -6190,28 +6187,28 @@
         <v>338</v>
       </c>
       <c r="C158" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D158" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E158" t="s">
         <v>6</v>
       </c>
       <c r="G158" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H158" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I158" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="J158" s="5" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>5</v>
       </c>
@@ -6219,28 +6216,28 @@
         <v>190</v>
       </c>
       <c r="C159" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="D159" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E159" t="s">
         <v>6</v>
       </c>
       <c r="G159" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H159" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I159" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="J159" s="5" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>5</v>
       </c>
@@ -6248,28 +6245,28 @@
         <v>268</v>
       </c>
       <c r="C160" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="D160" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E160" t="s">
         <v>6</v>
       </c>
       <c r="G160" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H160" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I160" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="J160" s="5" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>5</v>
       </c>
@@ -6277,25 +6274,25 @@
         <v>371</v>
       </c>
       <c r="C161" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="D161" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E161" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G161" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H161" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I161" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>5</v>
       </c>
@@ -6303,22 +6300,22 @@
         <v>7</v>
       </c>
       <c r="C162" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D162" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E162" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G162" t="s">
         <v>7</v>
       </c>
       <c r="H162" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I162" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
   </sheetData>
@@ -6334,21 +6331,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63392036-0DF4-41BC-932A-0EBA4F02E5CB}">
   <dimension ref="A1:J1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6365,19 +6362,19 @@
         <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
